--- a/research/traditional_assets/database/data/belgium/belgium_telecom_equipment.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_telecom_equipment.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1059545037396958</v>
+        <v>0.1057233674803465</v>
       </c>
       <c r="C2">
-        <v>446.0392862015559</v>
+        <v>442.6255624819428</v>
       </c>
       <c r="D2">
-        <v>376.2392862015559</v>
+        <v>377.3125624819428</v>
       </c>
       <c r="E2">
-        <v>-14.6</v>
+        <v>-10.113</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.487000000000001</v>
       </c>
       <c r="G2">
         <v>69.8</v>
@@ -1579,28 +1579,28 @@
         <v>42.9</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2256961</v>
       </c>
       <c r="N2">
-        <v>42.9</v>
+        <v>42.6743039</v>
       </c>
       <c r="O2">
-        <v>10.725</v>
+        <v>10.668575975</v>
       </c>
       <c r="P2">
-        <v>32.175</v>
+        <v>32.005727925</v>
       </c>
       <c r="Q2">
-        <v>40.475</v>
+        <v>40.30572792500001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1059545037396958</v>
+        <v>0.1064102196771177</v>
       </c>
       <c r="T2">
-        <v>1.172523243405601</v>
+        <v>1.181405995249583</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>190.07860570032</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1057233674803465</v>
+        <v>0.1054922312209973</v>
       </c>
       <c r="C3">
-        <v>442.6255624819428</v>
+        <v>439.2179796276724</v>
       </c>
       <c r="D3">
-        <v>377.3125624819428</v>
+        <v>378.3919796276724</v>
       </c>
       <c r="E3">
-        <v>-10.113</v>
+        <v>-5.625999999999999</v>
       </c>
       <c r="F3">
-        <v>4.487000000000001</v>
+        <v>8.974000000000002</v>
       </c>
       <c r="G3">
         <v>69.8</v>
@@ -1661,28 +1661,28 @@
         <v>42.9</v>
       </c>
       <c r="M3">
-        <v>0.2256961</v>
+        <v>0.4513922000000001</v>
       </c>
       <c r="N3">
-        <v>42.6743039</v>
+        <v>42.4486078</v>
       </c>
       <c r="O3">
-        <v>10.668575975</v>
+        <v>10.61215195</v>
       </c>
       <c r="P3">
-        <v>32.005727925</v>
+        <v>31.83645585</v>
       </c>
       <c r="Q3">
-        <v>40.30572792500001</v>
+        <v>40.13645585</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1064102196771177</v>
+        <v>0.1068752359397931</v>
       </c>
       <c r="T3">
-        <v>1.181405995249583</v>
+        <v>1.190470027743442</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>190.07860570032</v>
+        <v>95.03930285016</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1054922312209973</v>
+        <v>0.105261094961648</v>
       </c>
       <c r="C4">
-        <v>439.2179796276724</v>
+        <v>435.8165904933809</v>
       </c>
       <c r="D4">
-        <v>378.3919796276724</v>
+        <v>379.4775904933809</v>
       </c>
       <c r="E4">
-        <v>-5.625999999999999</v>
+        <v>-1.139000000000001</v>
       </c>
       <c r="F4">
-        <v>8.974000000000002</v>
+        <v>13.461</v>
       </c>
       <c r="G4">
         <v>69.8</v>
@@ -1743,28 +1743,28 @@
         <v>42.9</v>
       </c>
       <c r="M4">
-        <v>0.4513922000000001</v>
+        <v>0.6770883</v>
       </c>
       <c r="N4">
-        <v>42.4486078</v>
+        <v>42.2229117</v>
       </c>
       <c r="O4">
-        <v>10.61215195</v>
+        <v>10.555727925</v>
       </c>
       <c r="P4">
-        <v>31.83645585</v>
+        <v>31.667183775</v>
       </c>
       <c r="Q4">
-        <v>40.13645585</v>
+        <v>39.967183775</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1068752359397931</v>
+        <v>0.1073498401666474</v>
       </c>
       <c r="T4">
-        <v>1.190470027743442</v>
+        <v>1.199720947505216</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>95.03930285016</v>
+        <v>63.35953523344001</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.105261094961648</v>
+        <v>0.1050299587022988</v>
       </c>
       <c r="C5">
-        <v>435.8165904933809</v>
+        <v>432.4214485420119</v>
       </c>
       <c r="D5">
-        <v>379.4775904933809</v>
+        <v>380.5694485420119</v>
       </c>
       <c r="E5">
-        <v>-1.139000000000001</v>
+        <v>3.348000000000003</v>
       </c>
       <c r="F5">
-        <v>13.461</v>
+        <v>17.948</v>
       </c>
       <c r="G5">
         <v>69.8</v>
@@ -1825,28 +1825,28 @@
         <v>42.9</v>
       </c>
       <c r="M5">
-        <v>0.6770883</v>
+        <v>0.9027844000000002</v>
       </c>
       <c r="N5">
-        <v>42.2229117</v>
+        <v>41.9972156</v>
       </c>
       <c r="O5">
-        <v>10.555727925</v>
+        <v>10.4993039</v>
       </c>
       <c r="P5">
-        <v>31.667183775</v>
+        <v>31.4979117</v>
       </c>
       <c r="Q5">
-        <v>39.967183775</v>
+        <v>39.7979117</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1073498401666474</v>
+        <v>0.1078343319815612</v>
       </c>
       <c r="T5">
-        <v>1.199720947505216</v>
+        <v>1.209164594762026</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>63.35953523344001</v>
+        <v>47.51965142508</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1050299587022988</v>
+        <v>0.1047988224429496</v>
       </c>
       <c r="C6">
-        <v>432.4214485420119</v>
+        <v>429.0326078535929</v>
       </c>
       <c r="D6">
-        <v>380.5694485420119</v>
+        <v>381.6676078535929</v>
       </c>
       <c r="E6">
-        <v>3.348000000000003</v>
+        <v>7.835000000000001</v>
       </c>
       <c r="F6">
-        <v>17.948</v>
+        <v>22.435</v>
       </c>
       <c r="G6">
         <v>69.8</v>
@@ -1907,28 +1907,28 @@
         <v>42.9</v>
       </c>
       <c r="M6">
-        <v>0.9027844000000002</v>
+        <v>1.1284805</v>
       </c>
       <c r="N6">
-        <v>41.9972156</v>
+        <v>41.7715195</v>
       </c>
       <c r="O6">
-        <v>10.4993039</v>
+        <v>10.442879875</v>
       </c>
       <c r="P6">
-        <v>31.4979117</v>
+        <v>31.328639625</v>
       </c>
       <c r="Q6">
-        <v>39.7979117</v>
+        <v>39.62863962500001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1078343319815612</v>
+        <v>0.1083290236241574</v>
       </c>
       <c r="T6">
-        <v>1.209164594762026</v>
+        <v>1.218807055645296</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>47.51965142508</v>
+        <v>38.015721140064</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1047988224429496</v>
+        <v>0.1045676861836003</v>
       </c>
       <c r="C7">
-        <v>429.0326078535929</v>
+        <v>425.650123134165</v>
       </c>
       <c r="D7">
-        <v>381.6676078535929</v>
+        <v>382.772123134165</v>
       </c>
       <c r="E7">
-        <v>7.835000000000001</v>
+        <v>12.322</v>
       </c>
       <c r="F7">
-        <v>22.435</v>
+        <v>26.922</v>
       </c>
       <c r="G7">
         <v>69.8</v>
@@ -1989,28 +1989,28 @@
         <v>42.9</v>
       </c>
       <c r="M7">
-        <v>1.1284805</v>
+        <v>1.3541766</v>
       </c>
       <c r="N7">
-        <v>41.7715195</v>
+        <v>41.5458234</v>
       </c>
       <c r="O7">
-        <v>10.442879875</v>
+        <v>10.38645585</v>
       </c>
       <c r="P7">
-        <v>31.328639625</v>
+        <v>31.15936755</v>
       </c>
       <c r="Q7">
-        <v>39.62863962500001</v>
+        <v>39.45936755</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1083290236241574</v>
+        <v>0.1088342406208514</v>
       </c>
       <c r="T7">
-        <v>1.218807055645296</v>
+        <v>1.228654675270763</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.015721140064</v>
+        <v>31.67976761672</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1045676861836003</v>
+        <v>0.1043365499242511</v>
       </c>
       <c r="C8">
-        <v>425.650123134165</v>
+        <v>422.2740497248655</v>
       </c>
       <c r="D8">
-        <v>382.772123134165</v>
+        <v>383.8830497248655</v>
       </c>
       <c r="E8">
-        <v>12.322</v>
+        <v>16.809</v>
       </c>
       <c r="F8">
-        <v>26.922</v>
+        <v>31.409</v>
       </c>
       <c r="G8">
         <v>69.8</v>
@@ -2071,28 +2071,28 @@
         <v>42.9</v>
       </c>
       <c r="M8">
-        <v>1.3541766</v>
+        <v>1.5798727</v>
       </c>
       <c r="N8">
-        <v>41.5458234</v>
+        <v>41.3201273</v>
       </c>
       <c r="O8">
-        <v>10.38645585</v>
+        <v>10.330031825</v>
       </c>
       <c r="P8">
-        <v>31.15936755</v>
+        <v>30.990095475</v>
       </c>
       <c r="Q8">
-        <v>39.45936755</v>
+        <v>39.290095475</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1088342406208514</v>
+        <v>0.1093503224991947</v>
       </c>
       <c r="T8">
-        <v>1.228654675270763</v>
+        <v>1.238714071662369</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.67976761672</v>
+        <v>27.15408652861715</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1043365499242511</v>
+        <v>0.1041054136649018</v>
       </c>
       <c r="C9">
-        <v>422.2740497248655</v>
+        <v>418.9044436111733</v>
       </c>
       <c r="D9">
-        <v>383.8830497248655</v>
+        <v>385.0004436111734</v>
       </c>
       <c r="E9">
-        <v>16.809</v>
+        <v>21.29600000000001</v>
       </c>
       <c r="F9">
-        <v>31.40900000000001</v>
+        <v>35.89600000000001</v>
       </c>
       <c r="G9">
         <v>69.8</v>
@@ -2153,28 +2153,28 @@
         <v>42.9</v>
       </c>
       <c r="M9">
-        <v>1.5798727</v>
+        <v>1.8055688</v>
       </c>
       <c r="N9">
-        <v>41.3201273</v>
+        <v>41.0944312</v>
       </c>
       <c r="O9">
-        <v>10.330031825</v>
+        <v>10.2736078</v>
       </c>
       <c r="P9">
-        <v>30.990095475</v>
+        <v>30.82082339999999</v>
       </c>
       <c r="Q9">
-        <v>39.290095475</v>
+        <v>39.1208234</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1093503224991947</v>
+        <v>0.1098776235488063</v>
       </c>
       <c r="T9">
-        <v>1.238714071662369</v>
+        <v>1.248992150584228</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.15408652861714</v>
+        <v>23.75982571254</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1041054136649018</v>
+        <v>0.1038742774055526</v>
       </c>
       <c r="C10">
-        <v>418.9044436111733</v>
+        <v>415.5413614323124</v>
       </c>
       <c r="D10">
-        <v>385.0004436111734</v>
+        <v>386.1243614323124</v>
       </c>
       <c r="E10">
-        <v>21.29600000000001</v>
+        <v>25.783</v>
       </c>
       <c r="F10">
-        <v>35.89600000000001</v>
+        <v>40.383</v>
       </c>
       <c r="G10">
         <v>69.8</v>
@@ -2235,28 +2235,28 @@
         <v>42.9</v>
       </c>
       <c r="M10">
-        <v>1.8055688</v>
+        <v>2.0312649</v>
       </c>
       <c r="N10">
-        <v>41.0944312</v>
+        <v>40.86873509999999</v>
       </c>
       <c r="O10">
-        <v>10.2736078</v>
+        <v>10.217183775</v>
       </c>
       <c r="P10">
-        <v>30.82082339999999</v>
+        <v>30.651551325</v>
       </c>
       <c r="Q10">
-        <v>39.1208234</v>
+        <v>38.951551325</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1098776235488063</v>
+        <v>0.1104165136324754</v>
       </c>
       <c r="T10">
-        <v>1.248992150584228</v>
+        <v>1.259496121350522</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.75982571254</v>
+        <v>21.11984507781333</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1038742774055526</v>
+        <v>0.1036431411462033</v>
       </c>
       <c r="C11">
-        <v>415.5413614323124</v>
+        <v>412.1848604908225</v>
       </c>
       <c r="D11">
-        <v>386.1243614323124</v>
+        <v>387.2548604908225</v>
       </c>
       <c r="E11">
-        <v>25.783</v>
+        <v>30.27</v>
       </c>
       <c r="F11">
-        <v>40.383</v>
+        <v>44.87</v>
       </c>
       <c r="G11">
         <v>69.8</v>
@@ -2317,28 +2317,28 @@
         <v>42.9</v>
       </c>
       <c r="M11">
-        <v>2.0312649</v>
+        <v>2.256961</v>
       </c>
       <c r="N11">
-        <v>40.86873509999999</v>
+        <v>40.643039</v>
       </c>
       <c r="O11">
-        <v>10.217183775</v>
+        <v>10.16075975</v>
       </c>
       <c r="P11">
-        <v>30.651551325</v>
+        <v>30.48227925</v>
       </c>
       <c r="Q11">
-        <v>38.951551325</v>
+        <v>38.78227925</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1104165136324754</v>
+        <v>0.1109673790513371</v>
       </c>
       <c r="T11">
-        <v>1.259496121350522</v>
+        <v>1.270233513689401</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.11984507781333</v>
+        <v>19.00786057003201</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1036431411462033</v>
+        <v>0.1034120048868541</v>
       </c>
       <c r="C12">
-        <v>412.1848604908225</v>
+        <v>408.8349987622975</v>
       </c>
       <c r="D12">
-        <v>387.2548604908225</v>
+        <v>388.3919987622975</v>
       </c>
       <c r="E12">
-        <v>30.27</v>
+        <v>34.75700000000001</v>
       </c>
       <c r="F12">
-        <v>44.87</v>
+        <v>49.35700000000001</v>
       </c>
       <c r="G12">
         <v>69.8</v>
@@ -2399,28 +2399,28 @@
         <v>42.9</v>
       </c>
       <c r="M12">
-        <v>2.256961</v>
+        <v>2.4826571</v>
       </c>
       <c r="N12">
-        <v>40.643039</v>
+        <v>40.4173429</v>
       </c>
       <c r="O12">
-        <v>10.16075975</v>
+        <v>10.104335725</v>
       </c>
       <c r="P12">
-        <v>30.48227925</v>
+        <v>30.313007175</v>
       </c>
       <c r="Q12">
-        <v>38.78227925</v>
+        <v>38.61300717500001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1109673790513371</v>
+        <v>0.1115306234683754</v>
       </c>
       <c r="T12">
-        <v>1.270233513689401</v>
+        <v>1.281212195743761</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.007860570032</v>
+        <v>17.27987324548364</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1034120048868541</v>
+        <v>0.1031808686275049</v>
       </c>
       <c r="C13">
-        <v>408.8349987622975</v>
+        <v>405.4918349052977</v>
       </c>
       <c r="D13">
-        <v>388.3919987622975</v>
+        <v>389.5358349052976</v>
       </c>
       <c r="E13">
-        <v>34.75700000000001</v>
+        <v>39.244</v>
       </c>
       <c r="F13">
-        <v>49.35700000000001</v>
+        <v>53.844</v>
       </c>
       <c r="G13">
         <v>69.8</v>
@@ -2481,28 +2481,28 @@
         <v>42.9</v>
       </c>
       <c r="M13">
-        <v>2.4826571</v>
+        <v>2.7083532</v>
       </c>
       <c r="N13">
-        <v>40.4173429</v>
+        <v>40.1916468</v>
       </c>
       <c r="O13">
-        <v>10.104335725</v>
+        <v>10.0479117</v>
       </c>
       <c r="P13">
-        <v>30.313007175</v>
+        <v>30.1437351</v>
       </c>
       <c r="Q13">
-        <v>38.61300717500001</v>
+        <v>38.4437351</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1115306234683754</v>
+        <v>0.1121066688948919</v>
       </c>
       <c r="T13">
-        <v>1.281212195743761</v>
+        <v>1.292440393299356</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.27987324548364</v>
+        <v>15.83988380836</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1031808686275049</v>
+        <v>0.1029497323681556</v>
       </c>
       <c r="C14">
-        <v>405.4918349052977</v>
+        <v>402.1554282714342</v>
       </c>
       <c r="D14">
-        <v>389.5358349052976</v>
+        <v>390.6864282714342</v>
       </c>
       <c r="E14">
-        <v>39.244</v>
+        <v>43.73100000000001</v>
       </c>
       <c r="F14">
-        <v>53.844</v>
+        <v>58.33100000000001</v>
       </c>
       <c r="G14">
         <v>69.8</v>
@@ -2563,28 +2563,28 @@
         <v>42.9</v>
       </c>
       <c r="M14">
-        <v>2.7083532</v>
+        <v>2.9340493</v>
       </c>
       <c r="N14">
-        <v>40.1916468</v>
+        <v>39.9659507</v>
       </c>
       <c r="O14">
-        <v>10.0479117</v>
+        <v>9.991487675</v>
       </c>
       <c r="P14">
-        <v>30.1437351</v>
+        <v>29.974463025</v>
       </c>
       <c r="Q14">
-        <v>38.4437351</v>
+        <v>38.274463025</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1121066688948919</v>
+        <v>0.1126959567450065</v>
       </c>
       <c r="T14">
-        <v>1.292440393299356</v>
+        <v>1.303926710338988</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.83988380836</v>
+        <v>14.62143120771692</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1029497323681556</v>
+        <v>0.1027185961088064</v>
       </c>
       <c r="C15">
-        <v>402.1554282714342</v>
+        <v>398.8258389156371</v>
       </c>
       <c r="D15">
-        <v>390.6864282714342</v>
+        <v>391.8438389156371</v>
       </c>
       <c r="E15">
-        <v>43.73100000000001</v>
+        <v>48.21800000000001</v>
       </c>
       <c r="F15">
-        <v>58.33100000000001</v>
+        <v>62.81800000000001</v>
       </c>
       <c r="G15">
         <v>69.8</v>
@@ -2645,28 +2645,28 @@
         <v>42.9</v>
       </c>
       <c r="M15">
-        <v>2.9340493</v>
+        <v>3.1597454</v>
       </c>
       <c r="N15">
-        <v>39.9659507</v>
+        <v>39.7402546</v>
       </c>
       <c r="O15">
-        <v>9.991487675</v>
+        <v>9.93506365</v>
       </c>
       <c r="P15">
-        <v>29.974463025</v>
+        <v>29.80519095</v>
       </c>
       <c r="Q15">
-        <v>38.274463025</v>
+        <v>38.10519095000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1126959567450065</v>
+        <v>0.1132989489637284</v>
       </c>
       <c r="T15">
-        <v>1.303926710338988</v>
+        <v>1.315680151030704</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.62143120771692</v>
+        <v>13.57704326430857</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1027185961088064</v>
+        <v>0.1026562098494572</v>
       </c>
       <c r="C16">
-        <v>398.8258389156371</v>
+        <v>394.6524132017122</v>
       </c>
       <c r="D16">
-        <v>391.8438389156371</v>
+        <v>392.1574132017122</v>
       </c>
       <c r="E16">
-        <v>48.21800000000001</v>
+        <v>52.70500000000002</v>
       </c>
       <c r="F16">
-        <v>62.81800000000001</v>
+        <v>67.30500000000002</v>
       </c>
       <c r="G16">
         <v>69.8</v>
@@ -2727,45 +2727,45 @@
         <v>42.9</v>
       </c>
       <c r="M16">
-        <v>3.1597454</v>
+        <v>3.486399000000001</v>
       </c>
       <c r="N16">
-        <v>39.7402546</v>
+        <v>39.413601</v>
       </c>
       <c r="O16">
-        <v>9.93506365</v>
+        <v>9.85340025</v>
       </c>
       <c r="P16">
-        <v>29.80519095</v>
+        <v>29.56020075</v>
       </c>
       <c r="Q16">
-        <v>38.10519095000001</v>
+        <v>37.86020075</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1132989489637284</v>
+        <v>0.1139161292346555</v>
       </c>
       <c r="T16">
-        <v>1.315680151030704</v>
+        <v>1.327710143268108</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.57704326430857</v>
+        <v>12.30495993143642</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1026562098494572</v>
+        <v>0.1024363235901079</v>
       </c>
       <c r="C17">
-        <v>394.6524132017122</v>
+        <v>391.2746485005133</v>
       </c>
       <c r="D17">
-        <v>392.1574132017122</v>
+        <v>393.2666485005133</v>
       </c>
       <c r="E17">
-        <v>52.70500000000001</v>
+        <v>57.19200000000001</v>
       </c>
       <c r="F17">
-        <v>67.30500000000001</v>
+        <v>71.79200000000002</v>
       </c>
       <c r="G17">
         <v>69.8</v>
@@ -2809,28 +2809,28 @@
         <v>42.9</v>
       </c>
       <c r="M17">
-        <v>3.486399</v>
+        <v>3.718825600000001</v>
       </c>
       <c r="N17">
-        <v>39.413601</v>
+        <v>39.1811744</v>
       </c>
       <c r="O17">
-        <v>9.85340025</v>
+        <v>9.795293599999999</v>
       </c>
       <c r="P17">
-        <v>29.56020075</v>
+        <v>29.3858808</v>
       </c>
       <c r="Q17">
-        <v>37.86020075</v>
+        <v>37.6858808</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1139161292346555</v>
+        <v>0.114548004273938</v>
       </c>
       <c r="T17">
-        <v>1.327710143268108</v>
+        <v>1.340026563892116</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.30495993143642</v>
+        <v>11.53589993572164</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1024363235901079</v>
+        <v>0.1022164373307587</v>
       </c>
       <c r="C18">
-        <v>391.2746485005133</v>
+        <v>387.9031766451456</v>
       </c>
       <c r="D18">
-        <v>393.2666485005133</v>
+        <v>394.3821766451456</v>
       </c>
       <c r="E18">
-        <v>57.19200000000001</v>
+        <v>61.67900000000001</v>
       </c>
       <c r="F18">
-        <v>71.79200000000002</v>
+        <v>76.27900000000001</v>
       </c>
       <c r="G18">
         <v>69.8</v>
@@ -2891,28 +2891,28 @@
         <v>42.9</v>
       </c>
       <c r="M18">
-        <v>3.718825600000001</v>
+        <v>3.9512522</v>
       </c>
       <c r="N18">
-        <v>39.1811744</v>
+        <v>38.9487478</v>
       </c>
       <c r="O18">
-        <v>9.795293599999999</v>
+        <v>9.73718695</v>
       </c>
       <c r="P18">
-        <v>29.3858808</v>
+        <v>29.21156085</v>
       </c>
       <c r="Q18">
-        <v>37.6858808</v>
+        <v>37.51156085</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.114548004273938</v>
+        <v>0.1151951052177816</v>
       </c>
       <c r="T18">
-        <v>1.340026563892116</v>
+        <v>1.35263976573598</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.53589993572164</v>
+        <v>10.85731758656155</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1022164373307587</v>
+        <v>0.1019965510714094</v>
       </c>
       <c r="C19">
-        <v>387.9031766451456</v>
+        <v>384.5380513382227</v>
       </c>
       <c r="D19">
-        <v>394.3821766451456</v>
+        <v>395.5040513382227</v>
       </c>
       <c r="E19">
-        <v>61.67900000000001</v>
+        <v>66.16600000000003</v>
       </c>
       <c r="F19">
-        <v>76.27900000000001</v>
+        <v>80.76600000000002</v>
       </c>
       <c r="G19">
         <v>69.8</v>
@@ -2973,28 +2973,28 @@
         <v>42.9</v>
       </c>
       <c r="M19">
-        <v>3.9512522</v>
+        <v>4.183678800000001</v>
       </c>
       <c r="N19">
-        <v>38.9487478</v>
+        <v>38.7163212</v>
       </c>
       <c r="O19">
-        <v>9.73718695</v>
+        <v>9.679080299999999</v>
       </c>
       <c r="P19">
-        <v>29.21156085</v>
+        <v>29.0372409</v>
       </c>
       <c r="Q19">
-        <v>37.51156085</v>
+        <v>37.3372409</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1151951052177816</v>
+        <v>0.1158579891114749</v>
       </c>
       <c r="T19">
-        <v>1.35263976573598</v>
+        <v>1.365560606649207</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.85731758656155</v>
+        <v>10.25413327619701</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1019965510714095</v>
+        <v>0.1020189148120602</v>
       </c>
       <c r="C20">
-        <v>384.5380513382227</v>
+        <v>379.9366585267662</v>
       </c>
       <c r="D20">
-        <v>395.5040513382227</v>
+        <v>395.3896585267662</v>
       </c>
       <c r="E20">
-        <v>66.166</v>
+        <v>70.65300000000002</v>
       </c>
       <c r="F20">
-        <v>80.76600000000001</v>
+        <v>85.25300000000001</v>
       </c>
       <c r="G20">
         <v>69.8</v>
@@ -3055,45 +3055,45 @@
         <v>42.9</v>
       </c>
       <c r="M20">
-        <v>4.1836788</v>
+        <v>4.561035500000001</v>
       </c>
       <c r="N20">
-        <v>38.7163212</v>
+        <v>38.3389645</v>
       </c>
       <c r="O20">
-        <v>9.679080299999999</v>
+        <v>9.584741124999999</v>
       </c>
       <c r="P20">
-        <v>29.0372409</v>
+        <v>28.754223375</v>
       </c>
       <c r="Q20">
-        <v>37.3372409</v>
+        <v>37.054223375</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1158579891114749</v>
+        <v>0.1165372405087163</v>
       </c>
       <c r="T20">
-        <v>1.365560606649207</v>
+        <v>1.378800480671402</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.25413327619701</v>
+        <v>9.405758845770876</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1020189148120602</v>
+        <v>0.101811778552711</v>
       </c>
       <c r="C21">
-        <v>379.9366585267662</v>
+        <v>376.5117203206061</v>
       </c>
       <c r="D21">
-        <v>395.3896585267662</v>
+        <v>396.4517203206061</v>
       </c>
       <c r="E21">
-        <v>70.65300000000002</v>
+        <v>75.14000000000001</v>
       </c>
       <c r="F21">
-        <v>85.25300000000001</v>
+        <v>89.74000000000001</v>
       </c>
       <c r="G21">
         <v>69.8</v>
@@ -3137,28 +3137,28 @@
         <v>42.9</v>
       </c>
       <c r="M21">
-        <v>4.561035500000001</v>
+        <v>4.80109</v>
       </c>
       <c r="N21">
-        <v>38.3389645</v>
+        <v>38.09891</v>
       </c>
       <c r="O21">
-        <v>9.584741124999999</v>
+        <v>9.524727499999999</v>
       </c>
       <c r="P21">
-        <v>28.754223375</v>
+        <v>28.5741825</v>
       </c>
       <c r="Q21">
-        <v>37.054223375</v>
+        <v>36.8741825</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1165372405087163</v>
+        <v>0.1172334731908887</v>
       </c>
       <c r="T21">
-        <v>1.378800480671402</v>
+        <v>1.392371351544152</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.405758845770876</v>
+        <v>8.935470903482333</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.101811778552711</v>
+        <v>0.1016046422933617</v>
       </c>
       <c r="C22">
-        <v>376.5117203206061</v>
+        <v>373.0925031203474</v>
       </c>
       <c r="D22">
-        <v>396.4517203206061</v>
+        <v>397.5195031203474</v>
       </c>
       <c r="E22">
-        <v>75.14000000000001</v>
+        <v>79.62700000000001</v>
       </c>
       <c r="F22">
-        <v>89.74000000000001</v>
+        <v>94.22700000000002</v>
       </c>
       <c r="G22">
         <v>69.8</v>
@@ -3219,28 +3219,28 @@
         <v>42.9</v>
       </c>
       <c r="M22">
-        <v>4.80109</v>
+        <v>5.041144500000001</v>
       </c>
       <c r="N22">
-        <v>38.09891</v>
+        <v>37.8588555</v>
       </c>
       <c r="O22">
-        <v>9.524727499999999</v>
+        <v>9.464713874999999</v>
       </c>
       <c r="P22">
-        <v>28.5741825</v>
+        <v>28.394141625</v>
       </c>
       <c r="Q22">
-        <v>36.8741825</v>
+        <v>36.694141625</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1172334731908887</v>
+        <v>0.1179473320169136</v>
       </c>
       <c r="T22">
-        <v>1.392371351544152</v>
+        <v>1.406285788768111</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.935470903482333</v>
+        <v>8.509972289030793</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1016046422933617</v>
+        <v>0.1013975060340125</v>
       </c>
       <c r="C23">
-        <v>373.0925031203474</v>
+        <v>369.6790532768231</v>
       </c>
       <c r="D23">
-        <v>397.5195031203474</v>
+        <v>398.5930532768231</v>
       </c>
       <c r="E23">
-        <v>79.62700000000001</v>
+        <v>84.114</v>
       </c>
       <c r="F23">
-        <v>94.227</v>
+        <v>98.71400000000001</v>
       </c>
       <c r="G23">
         <v>69.8</v>
@@ -3301,28 +3301,28 @@
         <v>42.9</v>
       </c>
       <c r="M23">
-        <v>5.0411445</v>
+        <v>5.281199000000001</v>
       </c>
       <c r="N23">
-        <v>37.8588555</v>
+        <v>37.618801</v>
       </c>
       <c r="O23">
-        <v>9.464713874999999</v>
+        <v>9.404700249999999</v>
       </c>
       <c r="P23">
-        <v>28.394141625</v>
+        <v>28.21410075</v>
       </c>
       <c r="Q23">
-        <v>36.694141625</v>
+        <v>36.51410075</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1179473320169136</v>
+        <v>0.1186794949154006</v>
       </c>
       <c r="T23">
-        <v>1.406285788768111</v>
+        <v>1.420557006433709</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.509972289030795</v>
+        <v>8.12315536680212</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1013975060340125</v>
+        <v>0.1011903697746633</v>
       </c>
       <c r="C24">
-        <v>369.6790532768231</v>
+        <v>366.2714176429274</v>
       </c>
       <c r="D24">
-        <v>398.5930532768231</v>
+        <v>399.6724176429274</v>
       </c>
       <c r="E24">
-        <v>84.114</v>
+        <v>88.60100000000003</v>
       </c>
       <c r="F24">
-        <v>98.71400000000001</v>
+        <v>103.201</v>
       </c>
       <c r="G24">
         <v>69.8</v>
@@ -3383,28 +3383,28 @@
         <v>42.9</v>
       </c>
       <c r="M24">
-        <v>5.281199000000001</v>
+        <v>5.521253500000001</v>
       </c>
       <c r="N24">
-        <v>37.618801</v>
+        <v>37.3787465</v>
       </c>
       <c r="O24">
-        <v>9.404700249999999</v>
+        <v>9.344686625</v>
       </c>
       <c r="P24">
-        <v>28.21410075</v>
+        <v>28.034059875</v>
       </c>
       <c r="Q24">
-        <v>36.51410075</v>
+        <v>36.334059875</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1186794949154006</v>
+        <v>0.1194306750320302</v>
       </c>
       <c r="T24">
-        <v>1.420557006433709</v>
+        <v>1.435198905077635</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.12315536680212</v>
+        <v>7.769974698680289</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1011903697746633</v>
+        <v>0.101127233515314</v>
       </c>
       <c r="C25">
-        <v>366.2714176429274</v>
+        <v>362.1145771889343</v>
       </c>
       <c r="D25">
-        <v>399.6724176429274</v>
+        <v>400.0025771889343</v>
       </c>
       <c r="E25">
-        <v>88.60100000000003</v>
+        <v>93.08800000000002</v>
       </c>
       <c r="F25">
-        <v>103.201</v>
+        <v>107.688</v>
       </c>
       <c r="G25">
         <v>69.8</v>
@@ -3465,45 +3465,45 @@
         <v>42.9</v>
       </c>
       <c r="M25">
-        <v>5.521253500000001</v>
+        <v>5.847458400000001</v>
       </c>
       <c r="N25">
-        <v>37.3787465</v>
+        <v>37.0525416</v>
       </c>
       <c r="O25">
-        <v>9.344686625</v>
+        <v>9.263135399999999</v>
       </c>
       <c r="P25">
-        <v>28.034059875</v>
+        <v>27.7894062</v>
       </c>
       <c r="Q25">
-        <v>36.334059875</v>
+        <v>36.0894062</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1194306750320302</v>
+        <v>0.1202016230464658</v>
       </c>
       <c r="T25">
-        <v>1.435198905077635</v>
+        <v>1.45022611684377</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.769974698680289</v>
+        <v>7.336520769433776</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.101127233515314</v>
+        <v>0.1009260972559648</v>
       </c>
       <c r="C26">
-        <v>362.1145771889343</v>
+        <v>358.6830290201622</v>
       </c>
       <c r="D26">
-        <v>400.0025771889343</v>
+        <v>401.0580290201622</v>
       </c>
       <c r="E26">
-        <v>93.08799999999999</v>
+        <v>97.57500000000002</v>
       </c>
       <c r="F26">
-        <v>107.688</v>
+        <v>112.175</v>
       </c>
       <c r="G26">
         <v>69.8</v>
@@ -3547,28 +3547,28 @@
         <v>42.9</v>
       </c>
       <c r="M26">
-        <v>5.8474584</v>
+        <v>6.091102500000001</v>
       </c>
       <c r="N26">
-        <v>37.0525416</v>
+        <v>36.8088975</v>
       </c>
       <c r="O26">
-        <v>9.263135399999999</v>
+        <v>9.202224375</v>
       </c>
       <c r="P26">
-        <v>27.7894062</v>
+        <v>27.606673125</v>
       </c>
       <c r="Q26">
-        <v>36.0894062</v>
+        <v>35.906673125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1202016230464658</v>
+        <v>0.1209931296746197</v>
       </c>
       <c r="T26">
-        <v>1.45022611684377</v>
+        <v>1.465654054257002</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.336520769433776</v>
+        <v>7.043059938656425</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1009260972559648</v>
+        <v>0.1007249609966155</v>
       </c>
       <c r="C27">
-        <v>358.6830290201622</v>
+        <v>355.2570654439198</v>
       </c>
       <c r="D27">
-        <v>401.0580290201622</v>
+        <v>402.1190654439199</v>
       </c>
       <c r="E27">
-        <v>97.57500000000002</v>
+        <v>102.062</v>
       </c>
       <c r="F27">
-        <v>112.175</v>
+        <v>116.662</v>
       </c>
       <c r="G27">
         <v>69.8</v>
@@ -3629,28 +3629,28 @@
         <v>42.9</v>
       </c>
       <c r="M27">
-        <v>6.091102500000001</v>
+        <v>6.334746600000002</v>
       </c>
       <c r="N27">
-        <v>36.8088975</v>
+        <v>36.5652534</v>
       </c>
       <c r="O27">
-        <v>9.202224375</v>
+        <v>9.141313349999999</v>
       </c>
       <c r="P27">
-        <v>27.606673125</v>
+        <v>27.42394005</v>
       </c>
       <c r="Q27">
-        <v>35.906673125</v>
+        <v>35.72394005</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1209931296746197</v>
+        <v>0.1218060283738048</v>
       </c>
       <c r="T27">
-        <v>1.465654054257002</v>
+        <v>1.481498962951672</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.043059938656425</v>
+        <v>6.772173017938869</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1007249609966155</v>
+        <v>0.1005238247372663</v>
       </c>
       <c r="C28">
-        <v>355.2570654439198</v>
+        <v>351.8367309014622</v>
       </c>
       <c r="D28">
-        <v>402.1190654439199</v>
+        <v>403.1857309014622</v>
       </c>
       <c r="E28">
-        <v>102.062</v>
+        <v>106.549</v>
       </c>
       <c r="F28">
-        <v>116.662</v>
+        <v>121.149</v>
       </c>
       <c r="G28">
         <v>69.8</v>
@@ -3711,28 +3711,28 @@
         <v>42.9</v>
       </c>
       <c r="M28">
-        <v>6.334746600000002</v>
+        <v>6.578390700000001</v>
       </c>
       <c r="N28">
-        <v>36.5652534</v>
+        <v>36.3216093</v>
       </c>
       <c r="O28">
-        <v>9.141313349999999</v>
+        <v>9.080402325</v>
       </c>
       <c r="P28">
-        <v>27.42394005</v>
+        <v>27.241206975</v>
       </c>
       <c r="Q28">
-        <v>35.72394005</v>
+        <v>35.541206975</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1218060283738048</v>
+        <v>0.1226411982702278</v>
       </c>
       <c r="T28">
-        <v>1.481498962951672</v>
+        <v>1.497777978733868</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.772173017938869</v>
+        <v>6.521351795052245</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1005238247372663</v>
+        <v>0.100322688477917</v>
       </c>
       <c r="C29">
-        <v>351.8367309014622</v>
+        <v>348.4220703068395</v>
       </c>
       <c r="D29">
-        <v>403.1857309014622</v>
+        <v>404.2580703068395</v>
       </c>
       <c r="E29">
-        <v>106.549</v>
+        <v>111.036</v>
       </c>
       <c r="F29">
-        <v>121.149</v>
+        <v>125.636</v>
       </c>
       <c r="G29">
         <v>69.8</v>
@@ -3793,28 +3793,28 @@
         <v>42.9</v>
       </c>
       <c r="M29">
-        <v>6.578390700000001</v>
+        <v>6.822034800000002</v>
       </c>
       <c r="N29">
-        <v>36.3216093</v>
+        <v>36.07796519999999</v>
       </c>
       <c r="O29">
-        <v>9.080402325</v>
+        <v>9.019491299999999</v>
       </c>
       <c r="P29">
-        <v>27.241206975</v>
+        <v>27.0584739</v>
       </c>
       <c r="Q29">
-        <v>35.541206975</v>
+        <v>35.3584739</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1226411982702278</v>
+        <v>0.1234995673304403</v>
       </c>
       <c r="T29">
-        <v>1.497777978733868</v>
+        <v>1.514509189398902</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.521351795052245</v>
+        <v>6.288446373800378</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.100322688477917</v>
+        <v>0.1003390522185678</v>
       </c>
       <c r="C30">
-        <v>348.4220703068395</v>
+        <v>343.8476154232466</v>
       </c>
       <c r="D30">
-        <v>404.2580703068395</v>
+        <v>404.1706154232466</v>
       </c>
       <c r="E30">
-        <v>111.036</v>
+        <v>115.523</v>
       </c>
       <c r="F30">
-        <v>125.636</v>
+        <v>130.123</v>
       </c>
       <c r="G30">
         <v>69.8</v>
@@ -3875,45 +3875,45 @@
         <v>42.9</v>
       </c>
       <c r="M30">
-        <v>6.822034800000002</v>
+        <v>7.195801900000001</v>
       </c>
       <c r="N30">
-        <v>36.07796519999999</v>
+        <v>35.7041981</v>
       </c>
       <c r="O30">
-        <v>9.019491299999999</v>
+        <v>8.926049525</v>
       </c>
       <c r="P30">
-        <v>27.0584739</v>
+        <v>26.778148575</v>
       </c>
       <c r="Q30">
-        <v>35.3584739</v>
+        <v>35.078148575</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1234995673304403</v>
+        <v>0.1243821158007997</v>
       </c>
       <c r="T30">
-        <v>1.514509189398902</v>
+        <v>1.53171170177281</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.288446373800378</v>
+        <v>5.961809482276047</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1003390522185678</v>
+        <v>0.1001454159592186</v>
       </c>
       <c r="C31">
-        <v>343.8476154232466</v>
+        <v>340.3979226228363</v>
       </c>
       <c r="D31">
-        <v>404.1706154232466</v>
+        <v>405.2079226228363</v>
       </c>
       <c r="E31">
-        <v>115.523</v>
+        <v>120.01</v>
       </c>
       <c r="F31">
-        <v>130.123</v>
+        <v>134.61</v>
       </c>
       <c r="G31">
         <v>69.8</v>
@@ -3957,28 +3957,28 @@
         <v>42.9</v>
       </c>
       <c r="M31">
-        <v>7.195801899999999</v>
+        <v>7.443933000000001</v>
       </c>
       <c r="N31">
-        <v>35.7041981</v>
+        <v>35.456067</v>
       </c>
       <c r="O31">
-        <v>8.926049525</v>
+        <v>8.864016749999999</v>
       </c>
       <c r="P31">
-        <v>26.778148575</v>
+        <v>26.59205025</v>
       </c>
       <c r="Q31">
-        <v>35.078148575</v>
+        <v>34.89205025</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1243821158007997</v>
+        <v>0.1252898799417408</v>
       </c>
       <c r="T31">
-        <v>1.53171170177281</v>
+        <v>1.549405714500259</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.961809482276048</v>
+        <v>5.763082499533511</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1001454159592186</v>
+        <v>0.09995177969986932</v>
       </c>
       <c r="C32">
-        <v>340.3979226228363</v>
+        <v>336.9535680378718</v>
       </c>
       <c r="D32">
-        <v>405.2079226228363</v>
+        <v>406.2505680378718</v>
       </c>
       <c r="E32">
-        <v>120.01</v>
+        <v>124.497</v>
       </c>
       <c r="F32">
-        <v>134.61</v>
+        <v>139.097</v>
       </c>
       <c r="G32">
         <v>69.8</v>
@@ -4039,28 +4039,28 @@
         <v>42.9</v>
       </c>
       <c r="M32">
-        <v>7.443933000000001</v>
+        <v>7.692064100000001</v>
       </c>
       <c r="N32">
-        <v>35.456067</v>
+        <v>35.2079359</v>
       </c>
       <c r="O32">
-        <v>8.864016749999999</v>
+        <v>8.801983974999999</v>
       </c>
       <c r="P32">
-        <v>26.59205025</v>
+        <v>26.405951925</v>
       </c>
       <c r="Q32">
-        <v>34.89205025</v>
+        <v>34.705951925</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1252898799417408</v>
+        <v>0.1262239560867671</v>
       </c>
       <c r="T32">
-        <v>1.549405714500259</v>
+        <v>1.567612597161837</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.763082499533511</v>
+        <v>5.577176612451786</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09995177969986932</v>
+        <v>0.09975814344052009</v>
       </c>
       <c r="C33">
-        <v>336.9535680378718</v>
+        <v>333.5145929821384</v>
       </c>
       <c r="D33">
-        <v>406.2505680378718</v>
+        <v>407.2985929821384</v>
       </c>
       <c r="E33">
-        <v>124.497</v>
+        <v>128.984</v>
       </c>
       <c r="F33">
-        <v>139.097</v>
+        <v>143.584</v>
       </c>
       <c r="G33">
         <v>69.8</v>
@@ -4121,28 +4121,28 @@
         <v>42.9</v>
       </c>
       <c r="M33">
-        <v>7.692064100000001</v>
+        <v>7.940195200000002</v>
       </c>
       <c r="N33">
-        <v>35.2079359</v>
+        <v>34.95980479999999</v>
       </c>
       <c r="O33">
-        <v>8.801983974999999</v>
+        <v>8.739951199999998</v>
       </c>
       <c r="P33">
-        <v>26.405951925</v>
+        <v>26.21985359999999</v>
       </c>
       <c r="Q33">
-        <v>34.705951925</v>
+        <v>34.5198536</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1262239560867671</v>
+        <v>0.1271855050595884</v>
       </c>
       <c r="T33">
-        <v>1.567612597161837</v>
+        <v>1.586354976372284</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.577176612451786</v>
+        <v>5.402889843312666</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09975814344052009</v>
+        <v>0.09956450718117085</v>
       </c>
       <c r="C34">
-        <v>333.5145929821384</v>
+        <v>330.0810391968414</v>
       </c>
       <c r="D34">
-        <v>407.2985929821384</v>
+        <v>408.3520391968414</v>
       </c>
       <c r="E34">
-        <v>128.984</v>
+        <v>133.471</v>
       </c>
       <c r="F34">
-        <v>143.584</v>
+        <v>148.071</v>
       </c>
       <c r="G34">
         <v>69.8</v>
@@ -4203,28 +4203,28 @@
         <v>42.9</v>
       </c>
       <c r="M34">
-        <v>7.940195200000002</v>
+        <v>8.188326300000002</v>
       </c>
       <c r="N34">
-        <v>34.95980479999999</v>
+        <v>34.7116737</v>
       </c>
       <c r="O34">
-        <v>8.739951199999998</v>
+        <v>8.677918425</v>
       </c>
       <c r="P34">
-        <v>26.21985359999999</v>
+        <v>26.033755275</v>
       </c>
       <c r="Q34">
-        <v>34.5198536</v>
+        <v>34.333755275</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1271855050595884</v>
+        <v>0.1281757569868222</v>
       </c>
       <c r="T34">
-        <v>1.586354976372284</v>
+        <v>1.605656829589014</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.402889843312666</v>
+        <v>5.239165908666829</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09956450718117085</v>
+        <v>0.09937087092182162</v>
       </c>
       <c r="C35">
-        <v>330.0810391968414</v>
+        <v>326.6529488561473</v>
       </c>
       <c r="D35">
-        <v>408.3520391968414</v>
+        <v>409.4109488561473</v>
       </c>
       <c r="E35">
-        <v>133.471</v>
+        <v>137.958</v>
       </c>
       <c r="F35">
-        <v>148.071</v>
+        <v>152.558</v>
       </c>
       <c r="G35">
         <v>69.8</v>
@@ -4285,28 +4285,28 @@
         <v>42.9</v>
       </c>
       <c r="M35">
-        <v>8.188326300000002</v>
+        <v>8.436457400000002</v>
       </c>
       <c r="N35">
-        <v>34.7116737</v>
+        <v>34.4635426</v>
       </c>
       <c r="O35">
-        <v>8.677918425</v>
+        <v>8.615885649999999</v>
       </c>
       <c r="P35">
-        <v>26.033755275</v>
+        <v>25.84765695</v>
       </c>
       <c r="Q35">
-        <v>34.333755275</v>
+        <v>34.14765695</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1281757569868222</v>
+        <v>0.1291960165482146</v>
       </c>
       <c r="T35">
-        <v>1.605656829589014</v>
+        <v>1.625543587448675</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.239165908666829</v>
+        <v>5.085072793706039</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09937087092182162</v>
+        <v>0.09917723466247236</v>
       </c>
       <c r="C36">
-        <v>326.6529488561473</v>
+        <v>323.2303645728123</v>
       </c>
       <c r="D36">
-        <v>409.4109488561473</v>
+        <v>410.4753645728123</v>
       </c>
       <c r="E36">
-        <v>137.958</v>
+        <v>142.4450000000001</v>
       </c>
       <c r="F36">
-        <v>152.558</v>
+        <v>157.045</v>
       </c>
       <c r="G36">
         <v>69.8</v>
@@ -4367,28 +4367,28 @@
         <v>42.9</v>
       </c>
       <c r="M36">
-        <v>8.436457400000002</v>
+        <v>8.684588500000002</v>
       </c>
       <c r="N36">
-        <v>34.4635426</v>
+        <v>34.21541149999999</v>
       </c>
       <c r="O36">
-        <v>8.615885649999999</v>
+        <v>8.553852874999999</v>
       </c>
       <c r="P36">
-        <v>25.84765695</v>
+        <v>25.661558625</v>
       </c>
       <c r="Q36">
-        <v>34.14765695</v>
+        <v>33.961558625</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1291960165482146</v>
+        <v>0.130247668711496</v>
       </c>
       <c r="T36">
-        <v>1.625543587448675</v>
+        <v>1.646042245550171</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.085072793706039</v>
+        <v>4.939784999600152</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09917723466247236</v>
+        <v>0.09898359840312312</v>
       </c>
       <c r="C37">
-        <v>323.2303645728123</v>
+        <v>319.8133294038979</v>
       </c>
       <c r="D37">
-        <v>410.4753645728123</v>
+        <v>411.5453294038979</v>
       </c>
       <c r="E37">
-        <v>142.4450000000001</v>
+        <v>146.932</v>
       </c>
       <c r="F37">
-        <v>157.045</v>
+        <v>161.532</v>
       </c>
       <c r="G37">
         <v>69.8</v>
@@ -4449,28 +4449,28 @@
         <v>42.9</v>
       </c>
       <c r="M37">
-        <v>8.684588500000002</v>
+        <v>8.932719600000002</v>
       </c>
       <c r="N37">
-        <v>34.21541149999999</v>
+        <v>33.96728039999999</v>
       </c>
       <c r="O37">
-        <v>8.553852874999999</v>
+        <v>8.491820099999998</v>
       </c>
       <c r="P37">
-        <v>25.661558625</v>
+        <v>25.47546029999999</v>
       </c>
       <c r="Q37">
-        <v>33.961558625</v>
+        <v>33.7754603</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.130247668711496</v>
+        <v>0.1313321850048799</v>
       </c>
       <c r="T37">
-        <v>1.646042245550171</v>
+        <v>1.66718148671734</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.939784999600152</v>
+        <v>4.802568749611259</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09898359840312314</v>
+        <v>0.09878996214377389</v>
       </c>
       <c r="C38">
-        <v>319.8133294038979</v>
+        <v>316.4018868565782</v>
       </c>
       <c r="D38">
-        <v>411.5453294038979</v>
+        <v>412.6208868565782</v>
       </c>
       <c r="E38">
-        <v>146.932</v>
+        <v>151.419</v>
       </c>
       <c r="F38">
-        <v>161.532</v>
+        <v>166.019</v>
       </c>
       <c r="G38">
         <v>69.8</v>
@@ -4531,28 +4531,28 @@
         <v>42.9</v>
       </c>
       <c r="M38">
-        <v>8.9327196</v>
+        <v>9.180850700000001</v>
       </c>
       <c r="N38">
-        <v>33.9672804</v>
+        <v>33.7191493</v>
       </c>
       <c r="O38">
-        <v>8.4918201</v>
+        <v>8.429787324999999</v>
       </c>
       <c r="P38">
-        <v>25.4754603</v>
+        <v>25.289361975</v>
       </c>
       <c r="Q38">
-        <v>33.77546030000001</v>
+        <v>33.589361975</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1313321850048799</v>
+        <v>0.1324511303869427</v>
       </c>
       <c r="T38">
-        <v>1.66718148671734</v>
+        <v>1.688991814905688</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.802568749611261</v>
+        <v>4.672769594216361</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09878996214377389</v>
+        <v>0.09859632588442464</v>
       </c>
       <c r="C39">
-        <v>316.4018868565782</v>
+        <v>312.9960808940356</v>
       </c>
       <c r="D39">
-        <v>412.6208868565782</v>
+        <v>413.7020808940356</v>
       </c>
       <c r="E39">
-        <v>151.419</v>
+        <v>155.906</v>
       </c>
       <c r="F39">
-        <v>166.019</v>
+        <v>170.506</v>
       </c>
       <c r="G39">
         <v>69.8</v>
@@ -4613,28 +4613,28 @@
         <v>42.9</v>
       </c>
       <c r="M39">
-        <v>9.180850700000001</v>
+        <v>9.428981800000003</v>
       </c>
       <c r="N39">
-        <v>33.7191493</v>
+        <v>33.4710182</v>
       </c>
       <c r="O39">
-        <v>8.429787324999999</v>
+        <v>8.367754549999999</v>
       </c>
       <c r="P39">
-        <v>25.289361975</v>
+        <v>25.10326365</v>
       </c>
       <c r="Q39">
-        <v>33.589361975</v>
+        <v>33.40326365</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1324511303869427</v>
+        <v>0.1336061707813301</v>
       </c>
       <c r="T39">
-        <v>1.688991814905688</v>
+        <v>1.711505702067854</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.672769594216361</v>
+        <v>4.54980197331593</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09859632588442464</v>
+        <v>0.09913393962507541</v>
       </c>
       <c r="C40">
-        <v>312.9960808940356</v>
+        <v>305.5211143023116</v>
       </c>
       <c r="D40">
-        <v>413.7020808940356</v>
+        <v>410.7141143023117</v>
       </c>
       <c r="E40">
-        <v>155.906</v>
+        <v>160.393</v>
       </c>
       <c r="F40">
-        <v>170.506</v>
+        <v>174.993</v>
       </c>
       <c r="G40">
         <v>69.8</v>
@@ -4695,45 +4695,45 @@
         <v>42.9</v>
       </c>
       <c r="M40">
-        <v>9.428981800000003</v>
+        <v>10.1145954</v>
       </c>
       <c r="N40">
-        <v>33.4710182</v>
+        <v>32.78540459999999</v>
       </c>
       <c r="O40">
-        <v>8.367754549999999</v>
+        <v>8.196351149999998</v>
       </c>
       <c r="P40">
-        <v>25.10326365</v>
+        <v>24.58905344999999</v>
       </c>
       <c r="Q40">
-        <v>33.40326365</v>
+        <v>32.88905345</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1336061707813301</v>
+        <v>0.1347990813525826</v>
       </c>
       <c r="T40">
-        <v>1.711505702067854</v>
+        <v>1.734757749464845</v>
       </c>
       <c r="U40">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.54980197331593</v>
+        <v>4.241395557947873</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09913393962507541</v>
+        <v>0.09895905336572619</v>
       </c>
       <c r="C41">
-        <v>305.5211143023116</v>
+        <v>302.001354993733</v>
       </c>
       <c r="D41">
-        <v>410.7141143023117</v>
+        <v>411.681354993733</v>
       </c>
       <c r="E41">
-        <v>160.393</v>
+        <v>164.88</v>
       </c>
       <c r="F41">
-        <v>174.993</v>
+        <v>179.48</v>
       </c>
       <c r="G41">
         <v>69.8</v>
@@ -4777,28 +4777,28 @@
         <v>42.9</v>
       </c>
       <c r="M41">
-        <v>10.1145954</v>
+        <v>10.373944</v>
       </c>
       <c r="N41">
-        <v>32.78540459999999</v>
+        <v>32.526056</v>
       </c>
       <c r="O41">
-        <v>8.196351149999998</v>
+        <v>8.131513999999999</v>
       </c>
       <c r="P41">
-        <v>24.58905344999999</v>
+        <v>24.394542</v>
       </c>
       <c r="Q41">
-        <v>32.88905345</v>
+        <v>32.694542</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1347990813525826</v>
+        <v>0.1360317556095436</v>
       </c>
       <c r="T41">
-        <v>1.734757749464845</v>
+        <v>1.758784865108402</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.241395557947873</v>
+        <v>4.135360668999176</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09895905336572619</v>
+        <v>0.09878416710637694</v>
       </c>
       <c r="C42">
-        <v>302.001354993733</v>
+        <v>298.4861621851836</v>
       </c>
       <c r="D42">
-        <v>411.681354993733</v>
+        <v>412.6531621851836</v>
       </c>
       <c r="E42">
-        <v>164.88</v>
+        <v>169.367</v>
       </c>
       <c r="F42">
-        <v>179.48</v>
+        <v>183.967</v>
       </c>
       <c r="G42">
         <v>69.8</v>
@@ -4859,28 +4859,28 @@
         <v>42.9</v>
       </c>
       <c r="M42">
-        <v>10.373944</v>
+        <v>10.6332926</v>
       </c>
       <c r="N42">
-        <v>32.526056</v>
+        <v>32.26670739999999</v>
       </c>
       <c r="O42">
-        <v>8.131513999999999</v>
+        <v>8.066676849999999</v>
       </c>
       <c r="P42">
-        <v>24.394542</v>
+        <v>24.20003054999999</v>
       </c>
       <c r="Q42">
-        <v>32.694542</v>
+        <v>32.50003055</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1360317556095436</v>
+        <v>0.1373062154345372</v>
       </c>
       <c r="T42">
-        <v>1.758784865108402</v>
+        <v>1.783626459248352</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.135360668999176</v>
+        <v>4.034498213657733</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09878416710637694</v>
+        <v>0.0997117808470277</v>
       </c>
       <c r="C43">
-        <v>298.4861621851836</v>
+        <v>288.8963258483628</v>
       </c>
       <c r="D43">
-        <v>412.6531621851836</v>
+        <v>407.5503258483629</v>
       </c>
       <c r="E43">
-        <v>169.367</v>
+        <v>173.854</v>
       </c>
       <c r="F43">
-        <v>183.967</v>
+        <v>188.454</v>
       </c>
       <c r="G43">
         <v>69.8</v>
@@ -4941,45 +4941,45 @@
         <v>42.9</v>
       </c>
       <c r="M43">
-        <v>10.6332926</v>
+        <v>11.5522302</v>
       </c>
       <c r="N43">
-        <v>32.26670739999999</v>
+        <v>31.34776979999999</v>
       </c>
       <c r="O43">
-        <v>8.066676849999999</v>
+        <v>7.836942449999999</v>
       </c>
       <c r="P43">
-        <v>24.20003054999999</v>
+        <v>23.51082735</v>
       </c>
       <c r="Q43">
-        <v>32.50003055</v>
+        <v>31.81082735</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1373062154345372</v>
+        <v>0.1386246221500478</v>
       </c>
       <c r="T43">
-        <v>1.783626459248352</v>
+        <v>1.809324660082781</v>
       </c>
       <c r="U43">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.034498213657733</v>
+        <v>3.713568657937581</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0997117808470277</v>
+        <v>0.09956314458767847</v>
       </c>
       <c r="C44">
-        <v>288.8963258483629</v>
+        <v>285.2184714709128</v>
       </c>
       <c r="D44">
-        <v>407.5503258483629</v>
+        <v>408.3594714709128</v>
       </c>
       <c r="E44">
-        <v>173.854</v>
+        <v>178.341</v>
       </c>
       <c r="F44">
-        <v>188.454</v>
+        <v>192.941</v>
       </c>
       <c r="G44">
         <v>69.8</v>
@@ -5023,28 +5023,28 @@
         <v>42.9</v>
       </c>
       <c r="M44">
-        <v>11.5522302</v>
+        <v>11.8272833</v>
       </c>
       <c r="N44">
-        <v>31.3477698</v>
+        <v>31.0727167</v>
       </c>
       <c r="O44">
-        <v>7.83694245</v>
+        <v>7.768179175</v>
       </c>
       <c r="P44">
-        <v>23.51082735</v>
+        <v>23.304537525</v>
       </c>
       <c r="Q44">
-        <v>31.81082735</v>
+        <v>31.604537525</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1386246221500478</v>
+        <v>0.1399892887503131</v>
       </c>
       <c r="T44">
-        <v>1.809324660082781</v>
+        <v>1.83592455217456</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.713568657937581</v>
+        <v>3.62720659612508</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09956314458767847</v>
+        <v>0.09941450832832924</v>
       </c>
       <c r="C45">
-        <v>285.2184714709128</v>
+        <v>281.5438364214792</v>
       </c>
       <c r="D45">
-        <v>408.3594714709128</v>
+        <v>409.1718364214793</v>
       </c>
       <c r="E45">
-        <v>178.341</v>
+        <v>182.828</v>
       </c>
       <c r="F45">
-        <v>192.941</v>
+        <v>197.428</v>
       </c>
       <c r="G45">
         <v>69.8</v>
@@ -5105,28 +5105,28 @@
         <v>42.9</v>
       </c>
       <c r="M45">
-        <v>11.8272833</v>
+        <v>12.1023364</v>
       </c>
       <c r="N45">
-        <v>31.0727167</v>
+        <v>30.7976636</v>
       </c>
       <c r="O45">
-        <v>7.768179175</v>
+        <v>7.699415899999999</v>
       </c>
       <c r="P45">
-        <v>23.304537525</v>
+        <v>23.0982477</v>
       </c>
       <c r="Q45">
-        <v>31.604537525</v>
+        <v>31.3982477</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1399892887503131</v>
+        <v>0.1414026934434451</v>
       </c>
       <c r="T45">
-        <v>1.83592455217456</v>
+        <v>1.863474440412474</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.62720659612508</v>
+        <v>3.544770082576782</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09941450832832924</v>
+        <v>0.10021087206898</v>
       </c>
       <c r="C46">
-        <v>281.5438364214792</v>
+        <v>272.7416797895303</v>
       </c>
       <c r="D46">
-        <v>409.1718364214793</v>
+        <v>404.8566797895303</v>
       </c>
       <c r="E46">
-        <v>182.828</v>
+        <v>187.315</v>
       </c>
       <c r="F46">
-        <v>197.428</v>
+        <v>201.915</v>
       </c>
       <c r="G46">
         <v>69.8</v>
@@ -5187,45 +5187,45 @@
         <v>42.9</v>
       </c>
       <c r="M46">
-        <v>12.1023364</v>
+        <v>12.9427515</v>
       </c>
       <c r="N46">
-        <v>30.7976636</v>
+        <v>29.9572485</v>
       </c>
       <c r="O46">
-        <v>7.699415899999999</v>
+        <v>7.489312125</v>
       </c>
       <c r="P46">
-        <v>23.0982477</v>
+        <v>22.467936375</v>
       </c>
       <c r="Q46">
-        <v>31.3982477</v>
+        <v>30.76793637500001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1414026934434451</v>
+        <v>0.1428674946708727</v>
       </c>
       <c r="T46">
-        <v>1.863474440412474</v>
+        <v>1.89202614276813</v>
       </c>
       <c r="U46">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.544770082576782</v>
+        <v>3.314596590995353</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.10021087206898</v>
+        <v>0.1000832358096308</v>
       </c>
       <c r="C47">
-        <v>272.7416797895303</v>
+        <v>268.9401513194524</v>
       </c>
       <c r="D47">
-        <v>404.8566797895303</v>
+        <v>405.5421513194524</v>
       </c>
       <c r="E47">
-        <v>187.315</v>
+        <v>191.802</v>
       </c>
       <c r="F47">
-        <v>201.915</v>
+        <v>206.402</v>
       </c>
       <c r="G47">
         <v>69.8</v>
@@ -5269,28 +5269,28 @@
         <v>42.9</v>
       </c>
       <c r="M47">
-        <v>12.9427515</v>
+        <v>13.2303682</v>
       </c>
       <c r="N47">
-        <v>29.9572485</v>
+        <v>29.66963179999999</v>
       </c>
       <c r="O47">
-        <v>7.489312125</v>
+        <v>7.417407949999999</v>
       </c>
       <c r="P47">
-        <v>22.467936375</v>
+        <v>22.25222385</v>
       </c>
       <c r="Q47">
-        <v>30.76793637500001</v>
+        <v>30.55222385</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1428674946708727</v>
+        <v>0.1443865477956125</v>
       </c>
       <c r="T47">
-        <v>1.89202614276813</v>
+        <v>1.921635315581402</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.314596590995353</v>
+        <v>3.242540143365019</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1000832358096308</v>
+        <v>0.09995559955028152</v>
       </c>
       <c r="C48">
-        <v>268.9401513194524</v>
+        <v>265.1409479591731</v>
       </c>
       <c r="D48">
-        <v>405.5421513194524</v>
+        <v>406.2299479591732</v>
       </c>
       <c r="E48">
-        <v>191.802</v>
+        <v>196.289</v>
       </c>
       <c r="F48">
-        <v>206.402</v>
+        <v>210.889</v>
       </c>
       <c r="G48">
         <v>69.8</v>
@@ -5351,28 +5351,28 @@
         <v>42.9</v>
       </c>
       <c r="M48">
-        <v>13.2303682</v>
+        <v>13.5179849</v>
       </c>
       <c r="N48">
-        <v>29.66963179999999</v>
+        <v>29.3820151</v>
       </c>
       <c r="O48">
-        <v>7.417407949999999</v>
+        <v>7.345503774999999</v>
       </c>
       <c r="P48">
-        <v>22.25222385</v>
+        <v>22.036511325</v>
       </c>
       <c r="Q48">
-        <v>30.55222385</v>
+        <v>30.336511325</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1443865477956125</v>
+        <v>0.1459629236797764</v>
       </c>
       <c r="T48">
-        <v>1.921635315581402</v>
+        <v>1.952361815670647</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.242540143365019</v>
+        <v>3.173549927548742</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09995559955028152</v>
+        <v>0.09982796329093227</v>
       </c>
       <c r="C49">
-        <v>265.1409479591731</v>
+        <v>261.3440815589003</v>
       </c>
       <c r="D49">
-        <v>406.2299479591732</v>
+        <v>406.9200815589003</v>
       </c>
       <c r="E49">
-        <v>196.289</v>
+        <v>200.776</v>
       </c>
       <c r="F49">
-        <v>210.889</v>
+        <v>215.376</v>
       </c>
       <c r="G49">
         <v>69.8</v>
@@ -5433,28 +5433,28 @@
         <v>42.9</v>
       </c>
       <c r="M49">
-        <v>13.5179849</v>
+        <v>13.8056016</v>
       </c>
       <c r="N49">
-        <v>29.3820151</v>
+        <v>29.0943984</v>
       </c>
       <c r="O49">
-        <v>7.345503774999999</v>
+        <v>7.273599599999999</v>
       </c>
       <c r="P49">
-        <v>22.036511325</v>
+        <v>21.8207988</v>
       </c>
       <c r="Q49">
-        <v>30.336511325</v>
+        <v>30.1207988</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1459629236797764</v>
+        <v>0.147599929405639</v>
       </c>
       <c r="T49">
-        <v>1.952361815670647</v>
+        <v>1.984270104224864</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.173549927548742</v>
+        <v>3.107434304058143</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09982796329093227</v>
+        <v>0.09970032703158302</v>
       </c>
       <c r="C50">
-        <v>261.3440815589003</v>
+        <v>257.5495640495062</v>
       </c>
       <c r="D50">
-        <v>406.9200815589003</v>
+        <v>407.6125640495062</v>
       </c>
       <c r="E50">
-        <v>200.776</v>
+        <v>205.263</v>
       </c>
       <c r="F50">
-        <v>215.376</v>
+        <v>219.863</v>
       </c>
       <c r="G50">
         <v>69.8</v>
@@ -5515,28 +5515,28 @@
         <v>42.9</v>
       </c>
       <c r="M50">
-        <v>13.8056016</v>
+        <v>14.0932183</v>
       </c>
       <c r="N50">
-        <v>29.0943984</v>
+        <v>28.80678169999999</v>
       </c>
       <c r="O50">
-        <v>7.273599599999999</v>
+        <v>7.201695424999999</v>
       </c>
       <c r="P50">
-        <v>21.8207988</v>
+        <v>21.605086275</v>
       </c>
       <c r="Q50">
-        <v>30.1207988</v>
+        <v>29.905086275</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.147599929405639</v>
+        <v>0.1493011314344765</v>
       </c>
       <c r="T50">
-        <v>1.984270104224864</v>
+        <v>2.017429698212579</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.107434304058144</v>
+        <v>3.044017277444712</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09970032703158302</v>
+        <v>0.1024976907722338</v>
       </c>
       <c r="C51">
-        <v>257.5495640495062</v>
+        <v>238.4064456675603</v>
       </c>
       <c r="D51">
-        <v>407.6125640495062</v>
+        <v>392.9564456675603</v>
       </c>
       <c r="E51">
-        <v>205.263</v>
+        <v>209.75</v>
       </c>
       <c r="F51">
-        <v>219.863</v>
+        <v>224.35</v>
       </c>
       <c r="G51">
         <v>69.8</v>
@@ -5597,45 +5597,45 @@
         <v>42.9</v>
       </c>
       <c r="M51">
-        <v>14.0932183</v>
+        <v>16.130765</v>
       </c>
       <c r="N51">
-        <v>28.80678169999999</v>
+        <v>26.76923499999999</v>
       </c>
       <c r="O51">
-        <v>7.201695424999999</v>
+        <v>6.692308749999999</v>
       </c>
       <c r="P51">
-        <v>21.605086275</v>
+        <v>20.07692625</v>
       </c>
       <c r="Q51">
-        <v>29.905086275</v>
+        <v>28.37692625</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1493011314344765</v>
+        <v>0.1510703815444676</v>
       </c>
       <c r="T51">
-        <v>2.017429698212579</v>
+        <v>2.051915675959803</v>
       </c>
       <c r="U51">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.044017277444712</v>
+        <v>2.659514288379999</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1024976907722338</v>
+        <v>0.1024285545128845</v>
       </c>
       <c r="C52">
-        <v>238.4064456675603</v>
+        <v>234.2689550681432</v>
       </c>
       <c r="D52">
-        <v>392.9564456675603</v>
+        <v>393.3059550681432</v>
       </c>
       <c r="E52">
-        <v>209.75</v>
+        <v>214.237</v>
       </c>
       <c r="F52">
-        <v>224.35</v>
+        <v>228.837</v>
       </c>
       <c r="G52">
         <v>69.8</v>
@@ -5679,28 +5679,28 @@
         <v>42.9</v>
       </c>
       <c r="M52">
-        <v>16.130765</v>
+        <v>16.4533803</v>
       </c>
       <c r="N52">
-        <v>26.76923499999999</v>
+        <v>26.4466197</v>
       </c>
       <c r="O52">
-        <v>6.692308749999999</v>
+        <v>6.611654924999999</v>
       </c>
       <c r="P52">
-        <v>20.07692625</v>
+        <v>19.834964775</v>
       </c>
       <c r="Q52">
-        <v>28.37692625</v>
+        <v>28.134964775</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1510703815444676</v>
+        <v>0.1529118459446623</v>
       </c>
       <c r="T52">
-        <v>2.051915675959803</v>
+        <v>2.087809244635484</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.659514288379999</v>
+        <v>2.607366949392156</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1024285545128845</v>
+        <v>0.1023594182535353</v>
       </c>
       <c r="C53">
-        <v>234.2689550681432</v>
+        <v>230.1320867543244</v>
       </c>
       <c r="D53">
-        <v>393.3059550681432</v>
+        <v>393.6560867543245</v>
       </c>
       <c r="E53">
-        <v>214.237</v>
+        <v>218.724</v>
       </c>
       <c r="F53">
-        <v>228.837</v>
+        <v>233.324</v>
       </c>
       <c r="G53">
         <v>69.8</v>
@@ -5761,28 +5761,28 @@
         <v>42.9</v>
       </c>
       <c r="M53">
-        <v>16.4533803</v>
+        <v>16.77599560000001</v>
       </c>
       <c r="N53">
-        <v>26.4466197</v>
+        <v>26.12400439999999</v>
       </c>
       <c r="O53">
-        <v>6.611654924999999</v>
+        <v>6.531001099999998</v>
       </c>
       <c r="P53">
-        <v>19.834964775</v>
+        <v>19.5930033</v>
       </c>
       <c r="Q53">
-        <v>28.134964775</v>
+        <v>27.8930033</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1529118459446623</v>
+        <v>0.1548300380281986</v>
       </c>
       <c r="T53">
-        <v>2.087809244635484</v>
+        <v>2.125198378672652</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.607366949392156</v>
+        <v>2.55722527728846</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1023594182535353</v>
+        <v>0.1022902819941861</v>
       </c>
       <c r="C54">
-        <v>230.1320867543244</v>
+        <v>225.9958423895114</v>
       </c>
       <c r="D54">
-        <v>393.6560867543245</v>
+        <v>394.0068423895115</v>
       </c>
       <c r="E54">
-        <v>218.724</v>
+        <v>223.211</v>
       </c>
       <c r="F54">
-        <v>233.324</v>
+        <v>237.811</v>
       </c>
       <c r="G54">
         <v>69.8</v>
@@ -5843,28 +5843,28 @@
         <v>42.9</v>
       </c>
       <c r="M54">
-        <v>16.77599560000001</v>
+        <v>17.0986109</v>
       </c>
       <c r="N54">
-        <v>26.12400439999999</v>
+        <v>25.80138909999999</v>
       </c>
       <c r="O54">
-        <v>6.531001099999998</v>
+        <v>6.450347274999999</v>
       </c>
       <c r="P54">
-        <v>19.5930033</v>
+        <v>19.351041825</v>
       </c>
       <c r="Q54">
-        <v>27.8930033</v>
+        <v>27.651041825</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1548300380281986</v>
+        <v>0.1568298553067789</v>
       </c>
       <c r="T54">
-        <v>2.125198378672652</v>
+        <v>2.164178539690126</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.55722527728846</v>
+        <v>2.508975743754716</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1022902819941861</v>
+        <v>0.1038006457348368</v>
       </c>
       <c r="C55">
-        <v>225.9958423895114</v>
+        <v>213.9857805507929</v>
       </c>
       <c r="D55">
-        <v>394.0068423895115</v>
+        <v>386.4837805507929</v>
       </c>
       <c r="E55">
-        <v>223.211</v>
+        <v>227.698</v>
       </c>
       <c r="F55">
-        <v>237.811</v>
+        <v>242.298</v>
       </c>
       <c r="G55">
         <v>69.8</v>
@@ -5925,45 +5925,45 @@
         <v>42.9</v>
       </c>
       <c r="M55">
-        <v>17.0986109</v>
+        <v>18.3661884</v>
       </c>
       <c r="N55">
-        <v>25.80138909999999</v>
+        <v>24.5338116</v>
       </c>
       <c r="O55">
-        <v>6.450347274999999</v>
+        <v>6.133452899999999</v>
       </c>
       <c r="P55">
-        <v>19.351041825</v>
+        <v>18.4003587</v>
       </c>
       <c r="Q55">
-        <v>27.651041825</v>
+        <v>26.7003587</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1568298553067789</v>
+        <v>0.1589166211626888</v>
       </c>
       <c r="T55">
-        <v>2.164178539690126</v>
+        <v>2.204853490317055</v>
       </c>
       <c r="U55">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.508975743754716</v>
+        <v>2.33581400047056</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1038006457348368</v>
+        <v>0.1037607594754876</v>
       </c>
       <c r="C56">
-        <v>213.9857805507929</v>
+        <v>209.6937573514589</v>
       </c>
       <c r="D56">
-        <v>386.4837805507929</v>
+        <v>386.678757351459</v>
       </c>
       <c r="E56">
-        <v>227.698</v>
+        <v>232.1850000000001</v>
       </c>
       <c r="F56">
-        <v>242.298</v>
+        <v>246.7850000000001</v>
       </c>
       <c r="G56">
         <v>69.8</v>
@@ -6007,28 +6007,28 @@
         <v>42.9</v>
       </c>
       <c r="M56">
-        <v>18.3661884</v>
+        <v>18.70630300000001</v>
       </c>
       <c r="N56">
-        <v>24.5338116</v>
+        <v>24.19369699999999</v>
       </c>
       <c r="O56">
-        <v>6.133452899999999</v>
+        <v>6.048424249999998</v>
       </c>
       <c r="P56">
-        <v>18.4003587</v>
+        <v>18.14527275</v>
       </c>
       <c r="Q56">
-        <v>26.7003587</v>
+        <v>26.44527275</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1589166211626888</v>
+        <v>0.1610961321677502</v>
       </c>
       <c r="T56">
-        <v>2.204853490317055</v>
+        <v>2.247336216527403</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.33581400047056</v>
+        <v>2.293344655007458</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1037607594754876</v>
+        <v>0.1037208732161383</v>
       </c>
       <c r="C57">
-        <v>209.6937573514589</v>
+        <v>205.4019309787088</v>
       </c>
       <c r="D57">
-        <v>386.678757351459</v>
+        <v>386.8739309787088</v>
       </c>
       <c r="E57">
-        <v>232.1850000000001</v>
+        <v>236.6720000000001</v>
       </c>
       <c r="F57">
-        <v>246.7850000000001</v>
+        <v>251.272</v>
       </c>
       <c r="G57">
         <v>69.8</v>
@@ -6089,28 +6089,28 @@
         <v>42.9</v>
       </c>
       <c r="M57">
-        <v>18.70630300000001</v>
+        <v>19.04641760000001</v>
       </c>
       <c r="N57">
-        <v>24.19369699999999</v>
+        <v>23.85358239999999</v>
       </c>
       <c r="O57">
-        <v>6.048424249999998</v>
+        <v>5.963395599999998</v>
       </c>
       <c r="P57">
-        <v>18.14527275</v>
+        <v>17.8901868</v>
       </c>
       <c r="Q57">
-        <v>26.44527275</v>
+        <v>26.1901868</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1610961321677502</v>
+        <v>0.1633747118548599</v>
       </c>
       <c r="T57">
-        <v>2.247336216527403</v>
+        <v>2.291749975747312</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.293344655007458</v>
+        <v>2.252392071882325</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1037208732161383</v>
+        <v>0.1036809869567891</v>
       </c>
       <c r="C58">
-        <v>205.4019309787088</v>
+        <v>201.1103017307338</v>
       </c>
       <c r="D58">
-        <v>386.8739309787088</v>
+        <v>387.0693017307338</v>
       </c>
       <c r="E58">
-        <v>236.6720000000001</v>
+        <v>241.159</v>
       </c>
       <c r="F58">
-        <v>251.272</v>
+        <v>255.759</v>
       </c>
       <c r="G58">
         <v>69.8</v>
@@ -6171,28 +6171,28 @@
         <v>42.9</v>
       </c>
       <c r="M58">
-        <v>19.04641760000001</v>
+        <v>19.3865322</v>
       </c>
       <c r="N58">
-        <v>23.85358239999999</v>
+        <v>23.51346779999999</v>
       </c>
       <c r="O58">
-        <v>5.963395599999998</v>
+        <v>5.878366949999998</v>
       </c>
       <c r="P58">
-        <v>17.8901868</v>
+        <v>17.63510084999999</v>
       </c>
       <c r="Q58">
-        <v>26.1901868</v>
+        <v>25.93510085</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1633747118548599</v>
+        <v>0.1657592719925328</v>
       </c>
       <c r="T58">
-        <v>2.291749975747312</v>
+        <v>2.338229491210008</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.252392071882325</v>
+        <v>2.212876421498425</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1036809869567891</v>
+        <v>0.1036411006974399</v>
       </c>
       <c r="C59">
-        <v>201.1103017307338</v>
+        <v>196.818869906328</v>
       </c>
       <c r="D59">
-        <v>387.0693017307338</v>
+        <v>387.264869906328</v>
       </c>
       <c r="E59">
-        <v>241.159</v>
+        <v>245.646</v>
       </c>
       <c r="F59">
-        <v>255.759</v>
+        <v>260.246</v>
       </c>
       <c r="G59">
         <v>69.8</v>
@@ -6253,28 +6253,28 @@
         <v>42.9</v>
       </c>
       <c r="M59">
-        <v>19.3865322</v>
+        <v>19.7266468</v>
       </c>
       <c r="N59">
-        <v>23.51346779999999</v>
+        <v>23.17335319999999</v>
       </c>
       <c r="O59">
-        <v>5.878366949999998</v>
+        <v>5.793338299999998</v>
       </c>
       <c r="P59">
-        <v>17.63510084999999</v>
+        <v>17.3800149</v>
       </c>
       <c r="Q59">
-        <v>25.93510085</v>
+        <v>25.6800149</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1657592719925328</v>
+        <v>0.1682573826129521</v>
       </c>
       <c r="T59">
-        <v>2.338229491210008</v>
+        <v>2.386922316932832</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.212876421498425</v>
+        <v>2.174723379748452</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1036411006974399</v>
+        <v>0.1036012144380906</v>
       </c>
       <c r="C60">
-        <v>196.8188699063281</v>
+        <v>192.5276358048897</v>
       </c>
       <c r="D60">
-        <v>387.264869906328</v>
+        <v>387.4606358048896</v>
       </c>
       <c r="E60">
-        <v>245.646</v>
+        <v>250.133</v>
       </c>
       <c r="F60">
-        <v>260.246</v>
+        <v>264.733</v>
       </c>
       <c r="G60">
         <v>69.8</v>
@@ -6335,28 +6335,28 @@
         <v>42.9</v>
       </c>
       <c r="M60">
-        <v>19.7266468</v>
+        <v>20.0667614</v>
       </c>
       <c r="N60">
-        <v>23.1733532</v>
+        <v>22.8332386</v>
       </c>
       <c r="O60">
-        <v>5.793338299999999</v>
+        <v>5.708309649999999</v>
       </c>
       <c r="P60">
-        <v>17.3800149</v>
+        <v>17.12492895</v>
       </c>
       <c r="Q60">
-        <v>25.6800149</v>
+        <v>25.42492895</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1682573826129521</v>
+        <v>0.1708773522880259</v>
       </c>
       <c r="T60">
-        <v>2.386922316932831</v>
+        <v>2.437990402447013</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.174723379748452</v>
+        <v>2.137863661447631</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1036012144380906</v>
+        <v>0.1035613281787414</v>
       </c>
       <c r="C61">
-        <v>192.5276358048897</v>
+        <v>188.2365997264226</v>
       </c>
       <c r="D61">
-        <v>387.4606358048896</v>
+        <v>387.6565997264226</v>
       </c>
       <c r="E61">
-        <v>250.133</v>
+        <v>254.62</v>
       </c>
       <c r="F61">
-        <v>264.733</v>
+        <v>269.22</v>
       </c>
       <c r="G61">
         <v>69.8</v>
@@ -6417,28 +6417,28 @@
         <v>42.9</v>
       </c>
       <c r="M61">
-        <v>20.0667614</v>
+        <v>20.406876</v>
       </c>
       <c r="N61">
-        <v>22.8332386</v>
+        <v>22.49312399999999</v>
       </c>
       <c r="O61">
-        <v>5.708309649999999</v>
+        <v>5.623280999999999</v>
       </c>
       <c r="P61">
-        <v>17.12492895</v>
+        <v>16.869843</v>
       </c>
       <c r="Q61">
-        <v>25.42492895</v>
+        <v>25.169843</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1708773522880259</v>
+        <v>0.1736283204468535</v>
       </c>
       <c r="T61">
-        <v>2.437990402447013</v>
+        <v>2.491611892236903</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.137863661447631</v>
+        <v>2.102232600423504</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1035613281787414</v>
+        <v>0.1035214419193922</v>
       </c>
       <c r="C62">
-        <v>188.2365997264226</v>
+        <v>183.9457619715379</v>
       </c>
       <c r="D62">
-        <v>387.6565997264226</v>
+        <v>387.8527619715379</v>
       </c>
       <c r="E62">
-        <v>254.62</v>
+        <v>259.107</v>
       </c>
       <c r="F62">
-        <v>269.22</v>
+        <v>273.707</v>
       </c>
       <c r="G62">
         <v>69.8</v>
@@ -6499,28 +6499,28 @@
         <v>42.9</v>
       </c>
       <c r="M62">
-        <v>20.406876</v>
+        <v>20.7469906</v>
       </c>
       <c r="N62">
-        <v>22.49312399999999</v>
+        <v>22.1530094</v>
       </c>
       <c r="O62">
-        <v>5.623280999999999</v>
+        <v>5.53825235</v>
       </c>
       <c r="P62">
-        <v>16.869843</v>
+        <v>16.61475705</v>
       </c>
       <c r="Q62">
-        <v>25.169843</v>
+        <v>24.91475705</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1736283204468535</v>
+        <v>0.1765203638958773</v>
       </c>
       <c r="T62">
-        <v>2.491611892236903</v>
+        <v>2.547983202016019</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.102232600423504</v>
+        <v>2.067769770908365</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1035214419193922</v>
+        <v>0.1034815556600429</v>
       </c>
       <c r="C63">
-        <v>183.9457619715379</v>
+        <v>179.6551228414557</v>
       </c>
       <c r="D63">
-        <v>387.8527619715379</v>
+        <v>388.0491228414558</v>
       </c>
       <c r="E63">
-        <v>259.107</v>
+        <v>263.594</v>
       </c>
       <c r="F63">
-        <v>273.707</v>
+        <v>278.194</v>
       </c>
       <c r="G63">
         <v>69.8</v>
@@ -6581,28 +6581,28 @@
         <v>42.9</v>
       </c>
       <c r="M63">
-        <v>20.7469906</v>
+        <v>21.0871052</v>
       </c>
       <c r="N63">
-        <v>22.1530094</v>
+        <v>21.8128948</v>
       </c>
       <c r="O63">
-        <v>5.53825235</v>
+        <v>5.453223699999999</v>
       </c>
       <c r="P63">
-        <v>16.61475705</v>
+        <v>16.3596711</v>
       </c>
       <c r="Q63">
-        <v>24.91475705</v>
+        <v>24.6596711</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1765203638958773</v>
+        <v>0.1795646201580077</v>
       </c>
       <c r="T63">
-        <v>2.547983202016019</v>
+        <v>2.60732142283614</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.067769770908365</v>
+        <v>2.034418645571133</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1034815556600429</v>
+        <v>0.1034416694006937</v>
       </c>
       <c r="C64">
-        <v>179.6551228414557</v>
+        <v>175.3646826380059</v>
       </c>
       <c r="D64">
-        <v>388.0491228414558</v>
+        <v>388.245682638006</v>
       </c>
       <c r="E64">
-        <v>263.594</v>
+        <v>268.081</v>
       </c>
       <c r="F64">
-        <v>278.194</v>
+        <v>282.681</v>
       </c>
       <c r="G64">
         <v>69.8</v>
@@ -6663,28 +6663,28 @@
         <v>42.9</v>
       </c>
       <c r="M64">
-        <v>21.0871052</v>
+        <v>21.4272198</v>
       </c>
       <c r="N64">
-        <v>21.8128948</v>
+        <v>21.4727802</v>
       </c>
       <c r="O64">
-        <v>5.453223699999999</v>
+        <v>5.368195049999999</v>
       </c>
       <c r="P64">
-        <v>16.3596711</v>
+        <v>16.10458515</v>
       </c>
       <c r="Q64">
-        <v>24.6596711</v>
+        <v>24.40458515</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1795646201580077</v>
+        <v>0.1827734308126856</v>
       </c>
       <c r="T64">
-        <v>2.60732142283614</v>
+        <v>2.669867115051944</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.034418645571133</v>
+        <v>2.002126286117623</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1034416694006937</v>
+        <v>0.1102177831413444</v>
       </c>
       <c r="C65">
-        <v>175.3646826380059</v>
+        <v>140.1152246815395</v>
       </c>
       <c r="D65">
-        <v>388.245682638006</v>
+        <v>357.4832246815395</v>
       </c>
       <c r="E65">
-        <v>268.081</v>
+        <v>272.568</v>
       </c>
       <c r="F65">
-        <v>282.681</v>
+        <v>287.1680000000001</v>
       </c>
       <c r="G65">
         <v>69.8</v>
@@ -6745,45 +6745,45 @@
         <v>42.9</v>
       </c>
       <c r="M65">
-        <v>21.4272198</v>
+        <v>25.84512</v>
       </c>
       <c r="N65">
-        <v>21.4727802</v>
+        <v>17.05487999999999</v>
       </c>
       <c r="O65">
-        <v>5.368195049999999</v>
+        <v>4.263719999999998</v>
       </c>
       <c r="P65">
-        <v>16.10458515</v>
+        <v>12.79115999999999</v>
       </c>
       <c r="Q65">
-        <v>24.40458515</v>
+        <v>21.09116</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1827734308126856</v>
+        <v>0.1861605087259568</v>
       </c>
       <c r="T65">
-        <v>2.669867115051944</v>
+        <v>2.735887567946404</v>
       </c>
       <c r="U65">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V65">
         <v>0.25</v>
       </c>
       <c r="W65">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.002126286117623</v>
+        <v>1.659887824084392</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1102177831413444</v>
+        <v>0.1102843968819952</v>
       </c>
       <c r="C66">
-        <v>140.1152246815395</v>
+        <v>135.3499875758621</v>
       </c>
       <c r="D66">
-        <v>357.4832246815395</v>
+        <v>357.2049875758621</v>
       </c>
       <c r="E66">
-        <v>272.568</v>
+        <v>277.055</v>
       </c>
       <c r="F66">
-        <v>287.1680000000001</v>
+        <v>291.655</v>
       </c>
       <c r="G66">
         <v>69.8</v>
@@ -6827,28 +6827,28 @@
         <v>42.9</v>
       </c>
       <c r="M66">
-        <v>25.84512</v>
+        <v>26.24895</v>
       </c>
       <c r="N66">
-        <v>17.05487999999999</v>
+        <v>16.65105</v>
       </c>
       <c r="O66">
-        <v>4.263719999999998</v>
+        <v>4.162762499999999</v>
       </c>
       <c r="P66">
-        <v>12.79115999999999</v>
+        <v>12.4882875</v>
       </c>
       <c r="Q66">
-        <v>21.09116</v>
+        <v>20.7882875</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1861605087259568</v>
+        <v>0.1897411339485577</v>
       </c>
       <c r="T66">
-        <v>2.735887567946404</v>
+        <v>2.805680618149118</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.659887824084392</v>
+        <v>1.634351088329247</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1102843968819952</v>
+        <v>0.110351010622646</v>
       </c>
       <c r="C67">
-        <v>135.3499875758621</v>
+        <v>130.5851832495377</v>
       </c>
       <c r="D67">
-        <v>357.2049875758621</v>
+        <v>356.9271832495377</v>
       </c>
       <c r="E67">
-        <v>277.055</v>
+        <v>281.542</v>
       </c>
       <c r="F67">
-        <v>291.655</v>
+        <v>296.1420000000001</v>
       </c>
       <c r="G67">
         <v>69.8</v>
@@ -6909,28 +6909,28 @@
         <v>42.9</v>
       </c>
       <c r="M67">
-        <v>26.24895</v>
+        <v>26.65278</v>
       </c>
       <c r="N67">
-        <v>16.65105</v>
+        <v>16.24722</v>
       </c>
       <c r="O67">
-        <v>4.162762499999999</v>
+        <v>4.061804999999999</v>
       </c>
       <c r="P67">
-        <v>12.4882875</v>
+        <v>12.185415</v>
       </c>
       <c r="Q67">
-        <v>20.7882875</v>
+        <v>20.485415</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1897411339485577</v>
+        <v>0.1935323841842528</v>
       </c>
       <c r="T67">
-        <v>2.805680618149118</v>
+        <v>2.879579141893168</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.634351088329247</v>
+        <v>1.609588193051531</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.110351010622646</v>
+        <v>0.1104176243632967</v>
       </c>
       <c r="C68">
-        <v>130.5851832495377</v>
+        <v>125.8208106936116</v>
       </c>
       <c r="D68">
-        <v>356.9271832495377</v>
+        <v>356.6498106936117</v>
       </c>
       <c r="E68">
-        <v>281.542</v>
+        <v>286.0290000000001</v>
       </c>
       <c r="F68">
-        <v>296.1420000000001</v>
+        <v>300.6290000000001</v>
       </c>
       <c r="G68">
         <v>69.8</v>
@@ -6991,28 +6991,28 @@
         <v>42.9</v>
       </c>
       <c r="M68">
-        <v>26.65278</v>
+        <v>27.05661000000001</v>
       </c>
       <c r="N68">
-        <v>16.24722</v>
+        <v>15.84338999999999</v>
       </c>
       <c r="O68">
-        <v>4.061804999999999</v>
+        <v>3.960847499999998</v>
       </c>
       <c r="P68">
-        <v>12.185415</v>
+        <v>11.88254249999999</v>
       </c>
       <c r="Q68">
-        <v>20.485415</v>
+        <v>20.1825425</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1935323841842528</v>
+        <v>0.1975534071615052</v>
       </c>
       <c r="T68">
-        <v>2.879579141893168</v>
+        <v>2.957956364045949</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.609588193051531</v>
+        <v>1.585564488677628</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1104176243632967</v>
+        <v>0.1104842381039475</v>
       </c>
       <c r="C69">
-        <v>125.8208106936116</v>
+        <v>121.0568689022631</v>
       </c>
       <c r="D69">
-        <v>356.6498106936117</v>
+        <v>356.3728689022631</v>
       </c>
       <c r="E69">
-        <v>286.0290000000001</v>
+        <v>290.516</v>
       </c>
       <c r="F69">
-        <v>300.6290000000001</v>
+        <v>305.116</v>
       </c>
       <c r="G69">
         <v>69.8</v>
@@ -7073,28 +7073,28 @@
         <v>42.9</v>
       </c>
       <c r="M69">
-        <v>27.05661000000001</v>
+        <v>27.46044</v>
       </c>
       <c r="N69">
-        <v>15.84338999999999</v>
+        <v>15.43956</v>
       </c>
       <c r="O69">
-        <v>3.960847499999998</v>
+        <v>3.859889999999999</v>
       </c>
       <c r="P69">
-        <v>11.88254249999999</v>
+        <v>11.57967</v>
       </c>
       <c r="Q69">
-        <v>20.1825425</v>
+        <v>19.87967</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1975534071615052</v>
+        <v>0.2018257440748359</v>
       </c>
       <c r="T69">
-        <v>2.957956364045949</v>
+        <v>3.041232162583279</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.585564488677628</v>
+        <v>1.562247363844133</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1104842381039475</v>
+        <v>0.1105508518445982</v>
       </c>
       <c r="C70">
-        <v>121.0568689022631</v>
+        <v>116.2933568727929</v>
       </c>
       <c r="D70">
-        <v>356.3728689022631</v>
+        <v>356.096356872793</v>
       </c>
       <c r="E70">
-        <v>290.516</v>
+        <v>295.003</v>
       </c>
       <c r="F70">
-        <v>305.116</v>
+        <v>309.6030000000001</v>
       </c>
       <c r="G70">
         <v>69.8</v>
@@ -7155,28 +7155,28 @@
         <v>42.9</v>
       </c>
       <c r="M70">
-        <v>27.46044</v>
+        <v>27.86427</v>
       </c>
       <c r="N70">
-        <v>15.43956</v>
+        <v>15.03572999999999</v>
       </c>
       <c r="O70">
-        <v>3.859889999999999</v>
+        <v>3.758932499999998</v>
       </c>
       <c r="P70">
-        <v>11.57967</v>
+        <v>11.2767975</v>
       </c>
       <c r="Q70">
-        <v>19.87967</v>
+        <v>19.5767975</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2018257440748359</v>
+        <v>0.2063737156277363</v>
       </c>
       <c r="T70">
-        <v>3.041232162583279</v>
+        <v>3.129880593284307</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.562247363844133</v>
+        <v>1.539606097701465</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1105508518445982</v>
+        <v>0.110617465585249</v>
       </c>
       <c r="C71">
-        <v>116.2933568727929</v>
+        <v>111.5302736056114</v>
       </c>
       <c r="D71">
-        <v>356.096356872793</v>
+        <v>355.8202736056115</v>
       </c>
       <c r="E71">
-        <v>295.003</v>
+        <v>299.4900000000001</v>
       </c>
       <c r="F71">
-        <v>309.6030000000001</v>
+        <v>314.0900000000001</v>
       </c>
       <c r="G71">
         <v>69.8</v>
@@ -7237,28 +7237,28 @@
         <v>42.9</v>
       </c>
       <c r="M71">
-        <v>27.86427</v>
+        <v>28.26810000000001</v>
       </c>
       <c r="N71">
-        <v>15.03572999999999</v>
+        <v>14.63189999999999</v>
       </c>
       <c r="O71">
-        <v>3.758932499999998</v>
+        <v>3.657974999999998</v>
       </c>
       <c r="P71">
-        <v>11.2767975</v>
+        <v>10.97392499999999</v>
       </c>
       <c r="Q71">
-        <v>19.5767975</v>
+        <v>19.273925</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2063737156277363</v>
+        <v>0.2112248852841634</v>
       </c>
       <c r="T71">
-        <v>3.129880593284307</v>
+        <v>3.224438919365404</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.539606097701465</v>
+        <v>1.517611724877158</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.110617465585249</v>
+        <v>0.143967595313837</v>
       </c>
       <c r="C72">
-        <v>111.5302736056114</v>
+        <v>7.548862080729464</v>
       </c>
       <c r="D72">
-        <v>355.8202736056115</v>
+        <v>256.3258620807295</v>
       </c>
       <c r="E72">
-        <v>299.4900000000001</v>
+        <v>303.977</v>
       </c>
       <c r="F72">
-        <v>314.0900000000001</v>
+        <v>318.5770000000001</v>
       </c>
       <c r="G72">
         <v>69.8</v>
@@ -7319,45 +7319,45 @@
         <v>42.9</v>
       </c>
       <c r="M72">
-        <v>28.26810000000001</v>
+        <v>46.76710360000001</v>
       </c>
       <c r="N72">
-        <v>14.63189999999999</v>
+        <v>-3.867103600000014</v>
       </c>
       <c r="O72">
-        <v>3.657974999999998</v>
+        <v>-0.9667759000000036</v>
       </c>
       <c r="P72">
-        <v>10.97392499999999</v>
+        <v>-2.900327700000011</v>
       </c>
       <c r="Q72">
-        <v>19.273925</v>
+        <v>5.399672299999994</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2112248852841634</v>
+        <v>0.2194551033815596</v>
       </c>
       <c r="T72">
-        <v>3.224438919365404</v>
+        <v>3.384861188980546</v>
       </c>
       <c r="U72">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.25</v>
+        <v>0.2293278645547764</v>
       </c>
       <c r="W72">
-        <v>0.0675</v>
+        <v>0.1131346694833588</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y72">
-        <v>1.517611724877158</v>
+        <v>0.9173114582191056</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.143967595313837</v>
+        <v>0.144977595313837</v>
       </c>
       <c r="C73">
-        <v>7.548862080729521</v>
+        <v>0.9094666726788887</v>
       </c>
       <c r="D73">
-        <v>256.3258620807295</v>
+        <v>254.1734666726789</v>
       </c>
       <c r="E73">
-        <v>303.977</v>
+        <v>308.464</v>
       </c>
       <c r="F73">
-        <v>318.577</v>
+        <v>323.064</v>
       </c>
       <c r="G73">
         <v>69.8</v>
@@ -7401,37 +7401,37 @@
         <v>42.9</v>
       </c>
       <c r="M73">
-        <v>46.76710360000001</v>
+        <v>47.42579520000001</v>
       </c>
       <c r="N73">
-        <v>-3.867103600000007</v>
+        <v>-4.525795200000012</v>
       </c>
       <c r="O73">
-        <v>-0.9667759000000018</v>
+        <v>-1.131448800000003</v>
       </c>
       <c r="P73">
-        <v>-2.900327700000005</v>
+        <v>-3.394346400000009</v>
       </c>
       <c r="Q73">
-        <v>5.399672299999999</v>
+        <v>4.905653599999996</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2194551033815595</v>
+        <v>0.2256570713594724</v>
       </c>
       <c r="T73">
-        <v>3.384861188980545</v>
+        <v>3.505749088586993</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2293278645547765</v>
+        <v>0.226142755324849</v>
       </c>
       <c r="W73">
-        <v>0.1131346694833588</v>
+        <v>0.1136022435183122</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.9173114582191058</v>
+        <v>0.9045710212993959</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.144977595313837</v>
+        <v>0.145987595313837</v>
       </c>
       <c r="C74">
-        <v>0.9094666726788887</v>
+        <v>-5.694081960191397</v>
       </c>
       <c r="D74">
-        <v>254.1734666726789</v>
+        <v>252.0569180398086</v>
       </c>
       <c r="E74">
-        <v>308.464</v>
+        <v>312.951</v>
       </c>
       <c r="F74">
-        <v>323.064</v>
+        <v>327.551</v>
       </c>
       <c r="G74">
         <v>69.8</v>
@@ -7483,37 +7483,37 @@
         <v>42.9</v>
       </c>
       <c r="M74">
-        <v>47.42579520000001</v>
+        <v>48.08448680000001</v>
       </c>
       <c r="N74">
-        <v>-4.525795200000012</v>
+        <v>-5.184486800000009</v>
       </c>
       <c r="O74">
-        <v>-1.131448800000003</v>
+        <v>-1.296121700000002</v>
       </c>
       <c r="P74">
-        <v>-3.394346400000009</v>
+        <v>-3.888365100000007</v>
       </c>
       <c r="Q74">
-        <v>4.905653599999996</v>
+        <v>4.411634899999997</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2256570713594724</v>
+        <v>0.2323184443727862</v>
       </c>
       <c r="T74">
-        <v>3.505749088586993</v>
+        <v>3.635591647423548</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.226142755324849</v>
+        <v>0.2230449093614949</v>
       </c>
       <c r="W74">
-        <v>0.1136022435183122</v>
+        <v>0.1140570073057326</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.9045710212993959</v>
+        <v>0.8921796374459796</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.145987595313837</v>
+        <v>0.146997595313837</v>
       </c>
       <c r="C75">
-        <v>-5.694081960191397</v>
+        <v>-12.26267193023625</v>
       </c>
       <c r="D75">
-        <v>252.0569180398086</v>
+        <v>249.9753280697638</v>
       </c>
       <c r="E75">
-        <v>312.951</v>
+        <v>317.438</v>
       </c>
       <c r="F75">
-        <v>327.551</v>
+        <v>332.038</v>
       </c>
       <c r="G75">
         <v>69.8</v>
@@ -7565,37 +7565,37 @@
         <v>42.9</v>
       </c>
       <c r="M75">
-        <v>48.08448680000001</v>
+        <v>48.74317840000001</v>
       </c>
       <c r="N75">
-        <v>-5.184486800000009</v>
+        <v>-5.843178400000006</v>
       </c>
       <c r="O75">
-        <v>-1.296121700000002</v>
+        <v>-1.460794600000002</v>
       </c>
       <c r="P75">
-        <v>-3.888365100000007</v>
+        <v>-4.382383800000005</v>
       </c>
       <c r="Q75">
-        <v>4.411634899999997</v>
+        <v>3.917616199999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2323184443727862</v>
+        <v>0.2394922306948164</v>
       </c>
       <c r="T75">
-        <v>3.635591647423548</v>
+        <v>3.775422095401377</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2230449093614949</v>
+        <v>0.2200307889647179</v>
       </c>
       <c r="W75">
-        <v>0.1140570073057326</v>
+        <v>0.1144994801799794</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8921796374459796</v>
+        <v>0.8801231558588718</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.146997595313837</v>
+        <v>0.148007595313837</v>
       </c>
       <c r="C76">
-        <v>-12.26267193023625</v>
+        <v>-18.79716225251553</v>
       </c>
       <c r="D76">
-        <v>249.9753280697638</v>
+        <v>247.9278377474845</v>
       </c>
       <c r="E76">
-        <v>317.438</v>
+        <v>321.925</v>
       </c>
       <c r="F76">
-        <v>332.038</v>
+        <v>336.525</v>
       </c>
       <c r="G76">
         <v>69.8</v>
@@ -7647,37 +7647,37 @@
         <v>42.9</v>
       </c>
       <c r="M76">
-        <v>48.74317840000001</v>
+        <v>49.40187000000001</v>
       </c>
       <c r="N76">
-        <v>-5.843178400000006</v>
+        <v>-6.501870000000011</v>
       </c>
       <c r="O76">
-        <v>-1.460794600000002</v>
+        <v>-1.625467500000003</v>
       </c>
       <c r="P76">
-        <v>-4.382383800000005</v>
+        <v>-4.876402500000008</v>
       </c>
       <c r="Q76">
-        <v>3.917616199999999</v>
+        <v>3.423597499999996</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2394922306948164</v>
+        <v>0.2472399199226091</v>
       </c>
       <c r="T76">
-        <v>3.775422095401377</v>
+        <v>3.926438979217433</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2200307889647179</v>
+        <v>0.217097045111855</v>
       </c>
       <c r="W76">
-        <v>0.1144994801799794</v>
+        <v>0.1149301537775797</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8801231558588718</v>
+        <v>0.8683881804474201</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.148007595313837</v>
+        <v>0.149017595313837</v>
       </c>
       <c r="C77">
-        <v>-18.79716225251553</v>
+        <v>-25.29838402675966</v>
       </c>
       <c r="D77">
-        <v>247.9278377474845</v>
+        <v>245.9136159732404</v>
       </c>
       <c r="E77">
-        <v>321.925</v>
+        <v>326.412</v>
       </c>
       <c r="F77">
-        <v>336.525</v>
+        <v>341.0120000000001</v>
       </c>
       <c r="G77">
         <v>69.8</v>
@@ -7729,37 +7729,37 @@
         <v>42.9</v>
       </c>
       <c r="M77">
-        <v>49.40187000000001</v>
+        <v>50.06056160000001</v>
       </c>
       <c r="N77">
-        <v>-6.501870000000011</v>
+        <v>-7.160561600000015</v>
       </c>
       <c r="O77">
-        <v>-1.625467500000003</v>
+        <v>-1.790140400000004</v>
       </c>
       <c r="P77">
-        <v>-4.876402500000008</v>
+        <v>-5.370421200000012</v>
       </c>
       <c r="Q77">
-        <v>3.423597499999996</v>
+        <v>2.929578799999993</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2472399199226091</v>
+        <v>0.2556332499193845</v>
       </c>
       <c r="T77">
-        <v>3.926438979217433</v>
+        <v>4.090040603351492</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.217097045111855</v>
+        <v>0.2142405050445938</v>
       </c>
       <c r="W77">
-        <v>0.1149301537775797</v>
+        <v>0.1153494938594536</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8683881804474201</v>
+        <v>0.856962020178375</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.149017595313837</v>
+        <v>0.150027595313837</v>
       </c>
       <c r="C78">
-        <v>-25.29838402675966</v>
+        <v>-31.76714156218281</v>
       </c>
       <c r="D78">
-        <v>245.9136159732404</v>
+        <v>243.9318584378172</v>
       </c>
       <c r="E78">
-        <v>326.412</v>
+        <v>330.899</v>
       </c>
       <c r="F78">
-        <v>341.0120000000001</v>
+        <v>345.499</v>
       </c>
       <c r="G78">
         <v>69.8</v>
@@ -7811,37 +7811,37 @@
         <v>42.9</v>
       </c>
       <c r="M78">
-        <v>50.06056160000001</v>
+        <v>50.71925320000001</v>
       </c>
       <c r="N78">
-        <v>-7.160561600000015</v>
+        <v>-7.819253200000013</v>
       </c>
       <c r="O78">
-        <v>-1.790140400000004</v>
+        <v>-1.954813300000003</v>
       </c>
       <c r="P78">
-        <v>-5.370421200000012</v>
+        <v>-5.86443990000001</v>
       </c>
       <c r="Q78">
-        <v>2.929578799999993</v>
+        <v>2.435560099999995</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2556332499193845</v>
+        <v>0.2647564346984881</v>
       </c>
       <c r="T78">
-        <v>4.090040603351492</v>
+        <v>4.267868455671122</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2142405050445938</v>
+        <v>0.2114581608232354</v>
       </c>
       <c r="W78">
-        <v>0.1153494938594536</v>
+        <v>0.1157579419911491</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.856962020178375</v>
+        <v>0.8458326432929416</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.150027595313837</v>
+        <v>0.151037595313837</v>
       </c>
       <c r="C79">
-        <v>-31.76714156218281</v>
+        <v>-38.20421344834523</v>
       </c>
       <c r="D79">
-        <v>243.9318584378172</v>
+        <v>241.9817865516548</v>
       </c>
       <c r="E79">
-        <v>330.899</v>
+        <v>335.386</v>
       </c>
       <c r="F79">
-        <v>345.499</v>
+        <v>349.986</v>
       </c>
       <c r="G79">
         <v>69.8</v>
@@ -7893,37 +7893,37 @@
         <v>42.9</v>
       </c>
       <c r="M79">
-        <v>50.71925320000001</v>
+        <v>51.37794480000001</v>
       </c>
       <c r="N79">
-        <v>-7.819253200000013</v>
+        <v>-8.47794480000001</v>
       </c>
       <c r="O79">
-        <v>-1.954813300000003</v>
+        <v>-2.119486200000003</v>
       </c>
       <c r="P79">
-        <v>-5.86443990000001</v>
+        <v>-6.358458600000008</v>
       </c>
       <c r="Q79">
-        <v>2.435560099999995</v>
+        <v>1.941541399999997</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2647564346984881</v>
+        <v>0.2747089999120558</v>
       </c>
       <c r="T79">
-        <v>4.267868455671122</v>
+        <v>4.461862476383446</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2114581608232354</v>
+        <v>0.2087471587613991</v>
       </c>
       <c r="W79">
-        <v>0.1157579419911491</v>
+        <v>0.1161559170938266</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8458326432929416</v>
+        <v>0.8349886350455963</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.151037595313837</v>
+        <v>0.152047595313837</v>
       </c>
       <c r="C80">
-        <v>-38.20421344834523</v>
+        <v>-44.6103535750554</v>
       </c>
       <c r="D80">
-        <v>241.9817865516548</v>
+        <v>240.0626464249447</v>
       </c>
       <c r="E80">
-        <v>335.386</v>
+        <v>339.873</v>
       </c>
       <c r="F80">
-        <v>349.986</v>
+        <v>354.4730000000001</v>
       </c>
       <c r="G80">
         <v>69.8</v>
@@ -7975,37 +7975,37 @@
         <v>42.9</v>
       </c>
       <c r="M80">
-        <v>51.37794480000001</v>
+        <v>52.03663640000001</v>
       </c>
       <c r="N80">
-        <v>-8.47794480000001</v>
+        <v>-9.136636400000015</v>
       </c>
       <c r="O80">
-        <v>-2.119486200000003</v>
+        <v>-2.284159100000004</v>
       </c>
       <c r="P80">
-        <v>-6.358458600000008</v>
+        <v>-6.852477300000011</v>
       </c>
       <c r="Q80">
-        <v>1.941541399999997</v>
+        <v>1.447522699999993</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2747089999120558</v>
+        <v>0.2856094284792965</v>
       </c>
       <c r="T80">
-        <v>4.461862476383446</v>
+        <v>4.674332118115992</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2087471587613991</v>
+        <v>0.2061047896631535</v>
       </c>
       <c r="W80">
-        <v>0.1161559170938266</v>
+        <v>0.1165438168774491</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8349886350455963</v>
+        <v>0.8244191586526139</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.152047595313837</v>
+        <v>0.153057595313837</v>
       </c>
       <c r="C81">
-        <v>-44.6103535750554</v>
+        <v>-50.98629210412417</v>
       </c>
       <c r="D81">
-        <v>240.0626464249447</v>
+        <v>238.1737078958759</v>
       </c>
       <c r="E81">
-        <v>339.873</v>
+        <v>344.36</v>
       </c>
       <c r="F81">
-        <v>354.4730000000001</v>
+        <v>358.96</v>
       </c>
       <c r="G81">
         <v>69.8</v>
@@ -8057,37 +8057,37 @@
         <v>42.9</v>
       </c>
       <c r="M81">
-        <v>52.03663640000001</v>
+        <v>52.69532800000001</v>
       </c>
       <c r="N81">
-        <v>-9.136636400000015</v>
+        <v>-9.795328000000012</v>
       </c>
       <c r="O81">
-        <v>-2.284159100000004</v>
+        <v>-2.448832000000003</v>
       </c>
       <c r="P81">
-        <v>-6.852477300000011</v>
+        <v>-7.346496000000009</v>
       </c>
       <c r="Q81">
-        <v>1.447522699999993</v>
+        <v>0.9535039999999952</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2856094284792965</v>
+        <v>0.2975998999032614</v>
       </c>
       <c r="T81">
-        <v>4.674332118115992</v>
+        <v>4.908048724021791</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2061047896631535</v>
+        <v>0.2035284797923641</v>
       </c>
       <c r="W81">
-        <v>0.1165438168774491</v>
+        <v>0.116922019166481</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8244191586526139</v>
+        <v>0.8141139191694564</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.153057595313837</v>
+        <v>0.1540675953138371</v>
       </c>
       <c r="C82">
-        <v>-50.98629210412417</v>
+        <v>-57.33273639559769</v>
       </c>
       <c r="D82">
-        <v>238.1737078958759</v>
+        <v>236.3142636044024</v>
       </c>
       <c r="E82">
-        <v>344.36</v>
+        <v>348.847</v>
       </c>
       <c r="F82">
-        <v>358.96</v>
+        <v>363.4470000000001</v>
       </c>
       <c r="G82">
         <v>69.8</v>
@@ -8139,37 +8139,37 @@
         <v>42.9</v>
       </c>
       <c r="M82">
-        <v>52.69532800000001</v>
+        <v>53.35401960000002</v>
       </c>
       <c r="N82">
-        <v>-9.795328000000012</v>
+        <v>-10.45401960000002</v>
       </c>
       <c r="O82">
-        <v>-2.448832000000003</v>
+        <v>-2.613504900000004</v>
       </c>
       <c r="P82">
-        <v>-7.346496000000009</v>
+        <v>-7.840514700000012</v>
       </c>
       <c r="Q82">
-        <v>0.9535039999999952</v>
+        <v>0.4594852999999919</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2975998999032614</v>
+        <v>0.3108525262139594</v>
       </c>
       <c r="T82">
-        <v>4.908048724021791</v>
+        <v>5.166367077917676</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2035284797923641</v>
+        <v>0.2010157825109768</v>
       </c>
       <c r="W82">
-        <v>0.116922019166481</v>
+        <v>0.1172908831273886</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8141139191694564</v>
+        <v>0.8040631300439074</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1540675953138371</v>
+        <v>0.2019915807868866</v>
       </c>
       <c r="C83">
-        <v>-57.33273639559769</v>
+        <v>-125.6975433785603</v>
       </c>
       <c r="D83">
-        <v>236.3142636044024</v>
+        <v>172.4364566214397</v>
       </c>
       <c r="E83">
-        <v>348.847</v>
+        <v>353.3340000000001</v>
       </c>
       <c r="F83">
-        <v>363.4470000000001</v>
+        <v>367.9340000000001</v>
       </c>
       <c r="G83">
         <v>69.8</v>
@@ -8221,45 +8221,45 @@
         <v>42.9</v>
       </c>
       <c r="M83">
-        <v>53.35401960000002</v>
+        <v>73.88114720000002</v>
       </c>
       <c r="N83">
-        <v>-10.45401960000002</v>
+        <v>-30.98114720000002</v>
       </c>
       <c r="O83">
-        <v>-2.613504900000004</v>
+        <v>-7.745286800000004</v>
       </c>
       <c r="P83">
-        <v>-7.840514700000012</v>
+        <v>-23.23586040000001</v>
       </c>
       <c r="Q83">
-        <v>0.4594852999999919</v>
+        <v>-14.93586040000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3108525262139594</v>
+        <v>0.3402109191872323</v>
       </c>
       <c r="T83">
-        <v>5.166367077917676</v>
+        <v>5.738616801714871</v>
       </c>
       <c r="U83">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.2010157825109768</v>
+        <v>0.1451655856258821</v>
       </c>
       <c r="W83">
-        <v>0.1172908831273886</v>
+        <v>0.1716507504063229</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.8040631300439074</v>
+        <v>0.5806623425035282</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2019915807868866</v>
+        <v>0.2035415807868866</v>
       </c>
       <c r="C84">
-        <v>-125.6975433785603</v>
+        <v>-131.6790146669101</v>
       </c>
       <c r="D84">
-        <v>172.4364566214397</v>
+        <v>170.9419853330899</v>
       </c>
       <c r="E84">
-        <v>353.3340000000001</v>
+        <v>357.821</v>
       </c>
       <c r="F84">
-        <v>367.9340000000001</v>
+        <v>372.421</v>
       </c>
       <c r="G84">
         <v>69.8</v>
@@ -8303,37 +8303,37 @@
         <v>42.9</v>
       </c>
       <c r="M84">
-        <v>73.88114720000002</v>
+        <v>74.78213680000002</v>
       </c>
       <c r="N84">
-        <v>-30.98114720000002</v>
+        <v>-31.88213680000002</v>
       </c>
       <c r="O84">
-        <v>-7.745286800000004</v>
+        <v>-7.970534200000005</v>
       </c>
       <c r="P84">
-        <v>-23.23586040000001</v>
+        <v>-23.91160260000002</v>
       </c>
       <c r="Q84">
-        <v>-14.93586040000001</v>
+        <v>-15.61160260000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3402109191872323</v>
+        <v>0.3575292085511872</v>
       </c>
       <c r="T84">
-        <v>5.738616801714871</v>
+        <v>6.076182495933393</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1451655856258821</v>
+        <v>0.1434166026665341</v>
       </c>
       <c r="W84">
-        <v>0.1716507504063229</v>
+        <v>0.17200194618456</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5806623425035282</v>
+        <v>0.5736664106661364</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2035415807868866</v>
+        <v>0.2050915807868866</v>
       </c>
       <c r="C85">
-        <v>-131.6790146669101</v>
+        <v>-137.6348039853131</v>
       </c>
       <c r="D85">
-        <v>170.9419853330899</v>
+        <v>169.473196014687</v>
       </c>
       <c r="E85">
-        <v>357.821</v>
+        <v>362.308</v>
       </c>
       <c r="F85">
-        <v>372.421</v>
+        <v>376.9080000000001</v>
       </c>
       <c r="G85">
         <v>69.8</v>
@@ -8385,37 +8385,37 @@
         <v>42.9</v>
       </c>
       <c r="M85">
-        <v>74.78213680000002</v>
+        <v>75.68312640000002</v>
       </c>
       <c r="N85">
-        <v>-31.88213680000002</v>
+        <v>-32.78312640000002</v>
       </c>
       <c r="O85">
-        <v>-7.970534200000005</v>
+        <v>-8.195781600000005</v>
       </c>
       <c r="P85">
-        <v>-23.91160260000002</v>
+        <v>-24.58734480000002</v>
       </c>
       <c r="Q85">
-        <v>-15.61160260000001</v>
+        <v>-16.28734480000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3575292085511872</v>
+        <v>0.3770122840856365</v>
       </c>
       <c r="T85">
-        <v>6.076182495933393</v>
+        <v>6.455943901929232</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1434166026665341</v>
+        <v>0.1417092621585992</v>
       </c>
       <c r="W85">
-        <v>0.17200194618456</v>
+        <v>0.1723447801585533</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5736664106661364</v>
+        <v>0.5668370486343965</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2050915807868866</v>
+        <v>0.2066415807868866</v>
       </c>
       <c r="C86">
-        <v>-137.634803985313</v>
+        <v>-143.5655676976746</v>
       </c>
       <c r="D86">
-        <v>169.473196014687</v>
+        <v>168.0294323023254</v>
       </c>
       <c r="E86">
-        <v>362.308</v>
+        <v>366.795</v>
       </c>
       <c r="F86">
-        <v>376.908</v>
+        <v>381.395</v>
       </c>
       <c r="G86">
         <v>69.8</v>
@@ -8467,37 +8467,37 @@
         <v>42.9</v>
       </c>
       <c r="M86">
-        <v>75.68312640000001</v>
+        <v>76.58411600000001</v>
       </c>
       <c r="N86">
-        <v>-32.78312640000001</v>
+        <v>-33.68411600000001</v>
       </c>
       <c r="O86">
-        <v>-8.195781600000002</v>
+        <v>-8.421029000000003</v>
       </c>
       <c r="P86">
-        <v>-24.5873448</v>
+        <v>-25.26308700000001</v>
       </c>
       <c r="Q86">
-        <v>-16.2873448</v>
+        <v>-16.963087</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3770122840856363</v>
+        <v>0.3990931030246787</v>
       </c>
       <c r="T86">
-        <v>6.455943901929227</v>
+        <v>6.886340162057843</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1417092621585992</v>
+        <v>0.140042094368498</v>
       </c>
       <c r="W86">
-        <v>0.1723447801585533</v>
+        <v>0.1726795474508056</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5668370486343968</v>
+        <v>0.5601683774739921</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2066415807868866</v>
+        <v>0.2081915807868866</v>
       </c>
       <c r="C87">
-        <v>-143.5655676976746</v>
+        <v>-149.4719399902443</v>
       </c>
       <c r="D87">
-        <v>168.0294323023254</v>
+        <v>166.6100600097557</v>
       </c>
       <c r="E87">
-        <v>366.795</v>
+        <v>371.282</v>
       </c>
       <c r="F87">
-        <v>381.395</v>
+        <v>385.882</v>
       </c>
       <c r="G87">
         <v>69.8</v>
@@ -8549,37 +8549,37 @@
         <v>42.9</v>
       </c>
       <c r="M87">
-        <v>76.58411600000001</v>
+        <v>77.4851056</v>
       </c>
       <c r="N87">
-        <v>-33.68411600000001</v>
+        <v>-34.5851056</v>
       </c>
       <c r="O87">
-        <v>-8.421029000000003</v>
+        <v>-8.6462764</v>
       </c>
       <c r="P87">
-        <v>-25.26308700000001</v>
+        <v>-25.9388292</v>
       </c>
       <c r="Q87">
-        <v>-16.963087</v>
+        <v>-17.6388292</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3990931030246787</v>
+        <v>0.4243283246692986</v>
       </c>
       <c r="T87">
-        <v>6.886340162057843</v>
+        <v>7.378221602204832</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.140042094368498</v>
+        <v>0.1384136979223527</v>
       </c>
       <c r="W87">
-        <v>0.1726795474508056</v>
+        <v>0.1730065294571916</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5601683774739921</v>
+        <v>0.5536547916894108</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2081915807868866</v>
+        <v>0.2097415807868865</v>
       </c>
       <c r="C88">
-        <v>-149.4719399902443</v>
+        <v>-155.3545338004608</v>
       </c>
       <c r="D88">
-        <v>166.6100600097557</v>
+        <v>165.2144661995393</v>
       </c>
       <c r="E88">
-        <v>371.282</v>
+        <v>375.769</v>
       </c>
       <c r="F88">
-        <v>385.882</v>
+        <v>390.369</v>
       </c>
       <c r="G88">
         <v>69.8</v>
@@ -8631,37 +8631,37 @@
         <v>42.9</v>
       </c>
       <c r="M88">
-        <v>77.4851056</v>
+        <v>78.38609520000001</v>
       </c>
       <c r="N88">
-        <v>-34.5851056</v>
+        <v>-35.48609520000002</v>
       </c>
       <c r="O88">
-        <v>-8.6462764</v>
+        <v>-8.871523800000004</v>
       </c>
       <c r="P88">
-        <v>-25.9388292</v>
+        <v>-26.61457140000001</v>
       </c>
       <c r="Q88">
-        <v>-17.6388292</v>
+        <v>-18.31457140000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4243283246692986</v>
+        <v>0.4534458881053985</v>
       </c>
       <c r="T88">
-        <v>7.378221602204832</v>
+        <v>7.945777110066741</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1384136979223527</v>
+        <v>0.1368227358772682</v>
       </c>
       <c r="W88">
-        <v>0.1730065294571916</v>
+        <v>0.1733259946358446</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5536547916894108</v>
+        <v>0.5472909435090727</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2097415807868865</v>
+        <v>0.2112915807868866</v>
       </c>
       <c r="C89">
-        <v>-155.3545338004608</v>
+        <v>-161.2139416995032</v>
       </c>
       <c r="D89">
-        <v>165.2144661995393</v>
+        <v>163.8420583004969</v>
       </c>
       <c r="E89">
-        <v>375.769</v>
+        <v>380.256</v>
       </c>
       <c r="F89">
-        <v>390.369</v>
+        <v>394.8560000000001</v>
       </c>
       <c r="G89">
         <v>69.8</v>
@@ -8713,37 +8713,37 @@
         <v>42.9</v>
       </c>
       <c r="M89">
-        <v>78.38609520000001</v>
+        <v>79.28708480000002</v>
       </c>
       <c r="N89">
-        <v>-35.48609520000002</v>
+        <v>-36.38708480000002</v>
       </c>
       <c r="O89">
-        <v>-8.871523800000004</v>
+        <v>-9.096771200000004</v>
       </c>
       <c r="P89">
-        <v>-26.61457140000001</v>
+        <v>-27.29031360000001</v>
       </c>
       <c r="Q89">
-        <v>-18.31457140000001</v>
+        <v>-18.99031360000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4534458881053985</v>
+        <v>0.4874163787808485</v>
       </c>
       <c r="T89">
-        <v>7.945777110066741</v>
+        <v>8.607925202572305</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1368227358772682</v>
+        <v>0.135267932060481</v>
       </c>
       <c r="W89">
-        <v>0.1733259946358446</v>
+        <v>0.1736381992422554</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5472909435090727</v>
+        <v>0.5410717282419241</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2112915807868866</v>
+        <v>0.2128415807868866</v>
       </c>
       <c r="C90">
-        <v>-161.2139416995032</v>
+        <v>-167.0507367312167</v>
       </c>
       <c r="D90">
-        <v>163.8420583004969</v>
+        <v>162.4922632687834</v>
       </c>
       <c r="E90">
-        <v>380.256</v>
+        <v>384.7430000000001</v>
       </c>
       <c r="F90">
-        <v>394.8560000000001</v>
+        <v>399.3430000000001</v>
       </c>
       <c r="G90">
         <v>69.8</v>
@@ -8795,37 +8795,37 @@
         <v>42.9</v>
       </c>
       <c r="M90">
-        <v>79.28708480000002</v>
+        <v>80.18807440000002</v>
       </c>
       <c r="N90">
-        <v>-36.38708480000002</v>
+        <v>-37.28807440000002</v>
       </c>
       <c r="O90">
-        <v>-9.096771200000004</v>
+        <v>-9.322018600000005</v>
       </c>
       <c r="P90">
-        <v>-27.29031360000001</v>
+        <v>-27.96605580000001</v>
       </c>
       <c r="Q90">
-        <v>-18.99031360000001</v>
+        <v>-19.66605580000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4874163787808485</v>
+        <v>0.5275633223063801</v>
       </c>
       <c r="T90">
-        <v>8.607925202572305</v>
+        <v>9.390463857351605</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.135267932060481</v>
+        <v>0.1337480676553071</v>
       </c>
       <c r="W90">
-        <v>0.1736381992422554</v>
+        <v>0.1739433880148143</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5410717282419241</v>
+        <v>0.5349922706212282</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2128415807868866</v>
+        <v>0.2143915807868866</v>
       </c>
       <c r="C91">
-        <v>-167.0507367312167</v>
+        <v>-172.8654732099097</v>
       </c>
       <c r="D91">
-        <v>162.4922632687834</v>
+        <v>161.1645267900903</v>
       </c>
       <c r="E91">
-        <v>384.7430000000001</v>
+        <v>389.23</v>
       </c>
       <c r="F91">
-        <v>399.3430000000001</v>
+        <v>403.83</v>
       </c>
       <c r="G91">
         <v>69.8</v>
@@ -8877,37 +8877,37 @@
         <v>42.9</v>
       </c>
       <c r="M91">
-        <v>80.18807440000002</v>
+        <v>81.08906400000001</v>
       </c>
       <c r="N91">
-        <v>-37.28807440000002</v>
+        <v>-38.18906400000001</v>
       </c>
       <c r="O91">
-        <v>-9.322018600000005</v>
+        <v>-9.547266000000002</v>
       </c>
       <c r="P91">
-        <v>-27.96605580000001</v>
+        <v>-28.64179800000001</v>
       </c>
       <c r="Q91">
-        <v>-19.66605580000001</v>
+        <v>-20.341798</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5275633223063801</v>
+        <v>0.5757396545370181</v>
       </c>
       <c r="T91">
-        <v>9.390463857351605</v>
+        <v>10.32951024308677</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1337480676553071</v>
+        <v>0.1322619780146926</v>
       </c>
       <c r="W91">
-        <v>0.1739433880148143</v>
+        <v>0.1742417948146497</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5349922706212282</v>
+        <v>0.5290479120587703</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2143915807868866</v>
+        <v>0.2159415807868866</v>
       </c>
       <c r="C92">
-        <v>-172.8654732099097</v>
+        <v>-178.658687479354</v>
       </c>
       <c r="D92">
-        <v>161.1645267900903</v>
+        <v>159.8583125206461</v>
       </c>
       <c r="E92">
-        <v>389.23</v>
+        <v>393.717</v>
       </c>
       <c r="F92">
-        <v>403.83</v>
+        <v>408.3170000000001</v>
       </c>
       <c r="G92">
         <v>69.8</v>
@@ -8959,37 +8959,37 @@
         <v>42.9</v>
       </c>
       <c r="M92">
-        <v>81.08906400000001</v>
+        <v>81.99005360000001</v>
       </c>
       <c r="N92">
-        <v>-38.18906400000001</v>
+        <v>-39.09005360000001</v>
       </c>
       <c r="O92">
-        <v>-9.547266000000002</v>
+        <v>-9.772513400000003</v>
       </c>
       <c r="P92">
-        <v>-28.64179800000001</v>
+        <v>-29.31754020000001</v>
       </c>
       <c r="Q92">
-        <v>-20.341798</v>
+        <v>-21.01754020000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5757396545370181</v>
+        <v>0.6346218383744646</v>
       </c>
       <c r="T92">
-        <v>10.32951024308677</v>
+        <v>11.47723360342974</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1322619780146926</v>
+        <v>0.1308085496848608</v>
       </c>
       <c r="W92">
-        <v>0.1742417948146497</v>
+        <v>0.17453364322328</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5290479120587703</v>
+        <v>0.5232341987394431</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2159415807868866</v>
+        <v>0.2174915807868866</v>
       </c>
       <c r="C93">
-        <v>-178.658687479354</v>
+        <v>-184.4308986351721</v>
       </c>
       <c r="D93">
-        <v>159.8583125206461</v>
+        <v>158.5731013648279</v>
       </c>
       <c r="E93">
-        <v>393.717</v>
+        <v>398.2040000000001</v>
       </c>
       <c r="F93">
-        <v>408.3170000000001</v>
+        <v>412.8040000000001</v>
       </c>
       <c r="G93">
         <v>69.8</v>
@@ -9041,37 +9041,37 @@
         <v>42.9</v>
       </c>
       <c r="M93">
-        <v>81.99005360000001</v>
+        <v>82.89104320000003</v>
       </c>
       <c r="N93">
-        <v>-39.09005360000001</v>
+        <v>-39.99104320000003</v>
       </c>
       <c r="O93">
-        <v>-9.772513400000003</v>
+        <v>-9.997760800000007</v>
       </c>
       <c r="P93">
-        <v>-29.31754020000001</v>
+        <v>-29.99328240000002</v>
       </c>
       <c r="Q93">
-        <v>-21.01754020000001</v>
+        <v>-21.69328240000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6346218383744646</v>
+        <v>0.708224568171273</v>
       </c>
       <c r="T93">
-        <v>11.47723360342974</v>
+        <v>12.91188780385846</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1308085496848608</v>
+        <v>0.1293867176230688</v>
       </c>
       <c r="W93">
-        <v>0.17453364322328</v>
+        <v>0.1748191471012878</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5232341987394431</v>
+        <v>0.5175468704922752</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2174915807868866</v>
+        <v>0.2190415807868865</v>
       </c>
       <c r="C94">
-        <v>-184.4308986351721</v>
+        <v>-190.1826092126566</v>
       </c>
       <c r="D94">
-        <v>158.5731013648279</v>
+        <v>157.3083907873435</v>
       </c>
       <c r="E94">
-        <v>398.2040000000001</v>
+        <v>402.691</v>
       </c>
       <c r="F94">
-        <v>412.8040000000001</v>
+        <v>417.2910000000001</v>
       </c>
       <c r="G94">
         <v>69.8</v>
@@ -9123,37 +9123,37 @@
         <v>42.9</v>
       </c>
       <c r="M94">
-        <v>82.89104320000003</v>
+        <v>83.79203280000002</v>
       </c>
       <c r="N94">
-        <v>-39.99104320000003</v>
+        <v>-40.89203280000002</v>
       </c>
       <c r="O94">
-        <v>-9.997760800000007</v>
+        <v>-10.2230082</v>
       </c>
       <c r="P94">
-        <v>-29.99328240000002</v>
+        <v>-30.66902460000001</v>
       </c>
       <c r="Q94">
-        <v>-21.69328240000002</v>
+        <v>-22.36902460000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.708224568171273</v>
+        <v>0.8028566493385977</v>
       </c>
       <c r="T94">
-        <v>12.91188780385846</v>
+        <v>14.75644320440967</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1293867176230688</v>
+        <v>0.1279954625948638</v>
       </c>
       <c r="W94">
-        <v>0.1748191471012878</v>
+        <v>0.1750985111109513</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5175468704922752</v>
+        <v>0.5119818503794551</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2190415807868865</v>
+        <v>0.2205915807868866</v>
       </c>
       <c r="C95">
-        <v>-190.1826092126566</v>
+        <v>-195.914305841935</v>
       </c>
       <c r="D95">
-        <v>157.3083907873435</v>
+        <v>156.0636941580651</v>
       </c>
       <c r="E95">
-        <v>402.691</v>
+        <v>407.1780000000001</v>
       </c>
       <c r="F95">
-        <v>417.2910000000001</v>
+        <v>421.7780000000001</v>
       </c>
       <c r="G95">
         <v>69.8</v>
@@ -9205,37 +9205,37 @@
         <v>42.9</v>
       </c>
       <c r="M95">
-        <v>83.79203280000002</v>
+        <v>84.69302240000002</v>
       </c>
       <c r="N95">
-        <v>-40.89203280000002</v>
+        <v>-41.79302240000002</v>
       </c>
       <c r="O95">
-        <v>-10.2230082</v>
+        <v>-10.4482556</v>
       </c>
       <c r="P95">
-        <v>-30.66902460000001</v>
+        <v>-31.34476680000002</v>
       </c>
       <c r="Q95">
-        <v>-22.36902460000001</v>
+        <v>-23.04476680000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8028566493385977</v>
+        <v>0.9290327575616977</v>
       </c>
       <c r="T95">
-        <v>14.75644320440967</v>
+        <v>17.21585040514463</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1279954625948638</v>
+        <v>0.1266338087374716</v>
       </c>
       <c r="W95">
-        <v>0.1750985111109513</v>
+        <v>0.1753719312055157</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5119818503794551</v>
+        <v>0.5065352349498864</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2205915807868866</v>
+        <v>0.2221415807868866</v>
       </c>
       <c r="C96">
-        <v>-195.914305841935</v>
+        <v>-201.6264598722747</v>
       </c>
       <c r="D96">
-        <v>156.0636941580651</v>
+        <v>154.8385401277254</v>
       </c>
       <c r="E96">
-        <v>407.1780000000001</v>
+        <v>411.6650000000001</v>
       </c>
       <c r="F96">
-        <v>421.7780000000001</v>
+        <v>426.2650000000001</v>
       </c>
       <c r="G96">
         <v>69.8</v>
@@ -9287,37 +9287,37 @@
         <v>42.9</v>
       </c>
       <c r="M96">
-        <v>84.69302240000002</v>
+        <v>85.59401200000002</v>
       </c>
       <c r="N96">
-        <v>-41.79302240000002</v>
+        <v>-42.69401200000002</v>
       </c>
       <c r="O96">
-        <v>-10.4482556</v>
+        <v>-10.67350300000001</v>
       </c>
       <c r="P96">
-        <v>-31.34476680000002</v>
+        <v>-32.02050900000002</v>
       </c>
       <c r="Q96">
-        <v>-23.04476680000001</v>
+        <v>-23.72050900000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9290327575616977</v>
+        <v>1.105679309074038</v>
       </c>
       <c r="T96">
-        <v>17.21585040514463</v>
+        <v>20.65902048617356</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1266338087374716</v>
+        <v>0.1253008212770771</v>
       </c>
       <c r="W96">
-        <v>0.1753719312055157</v>
+        <v>0.1756395950875629</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5065352349498864</v>
+        <v>0.5012032851083086</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2221415807868866</v>
+        <v>0.2583544257402784</v>
       </c>
       <c r="C97">
-        <v>-201.6264598722747</v>
+        <v>-230.1108545728401</v>
       </c>
       <c r="D97">
-        <v>154.8385401277254</v>
+        <v>130.84114542716</v>
       </c>
       <c r="E97">
-        <v>411.6650000000001</v>
+        <v>416.152</v>
       </c>
       <c r="F97">
-        <v>426.2650000000001</v>
+        <v>430.7520000000001</v>
       </c>
       <c r="G97">
         <v>69.8</v>
@@ -9369,45 +9369,45 @@
         <v>42.9</v>
       </c>
       <c r="M97">
-        <v>85.59401200000002</v>
+        <v>101.5713216</v>
       </c>
       <c r="N97">
-        <v>-42.69401200000002</v>
+        <v>-58.67132160000002</v>
       </c>
       <c r="O97">
-        <v>-10.67350300000001</v>
+        <v>-14.66783040000001</v>
       </c>
       <c r="P97">
-        <v>-32.02050900000002</v>
+        <v>-44.00349120000001</v>
       </c>
       <c r="Q97">
-        <v>-23.72050900000001</v>
+        <v>-35.70349120000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.105679309074038</v>
+        <v>1.397220260177343</v>
       </c>
       <c r="T97">
-        <v>20.65902048617356</v>
+        <v>26.3416962680639</v>
       </c>
       <c r="U97">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1253008212770771</v>
+        <v>0.1055908285040962</v>
       </c>
       <c r="W97">
-        <v>0.1756395950875629</v>
+        <v>0.2109016826387341</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.5012032851083086</v>
+        <v>0.4223633140163846</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2583544257402783</v>
+        <v>0.2602544257402784</v>
       </c>
       <c r="C98">
-        <v>-230.11085457284</v>
+        <v>-235.6532205568467</v>
       </c>
       <c r="D98">
-        <v>130.84114542716</v>
+        <v>129.7857794431534</v>
       </c>
       <c r="E98">
-        <v>416.152</v>
+        <v>420.639</v>
       </c>
       <c r="F98">
-        <v>430.752</v>
+        <v>435.239</v>
       </c>
       <c r="G98">
         <v>69.8</v>
@@ -9451,37 +9451,37 @@
         <v>42.9</v>
       </c>
       <c r="M98">
-        <v>101.5713216</v>
+        <v>102.6293562</v>
       </c>
       <c r="N98">
-        <v>-58.67132160000001</v>
+        <v>-59.72935620000002</v>
       </c>
       <c r="O98">
-        <v>-14.6678304</v>
+        <v>-14.93233905</v>
       </c>
       <c r="P98">
-        <v>-44.00349120000001</v>
+        <v>-44.79701715000002</v>
       </c>
       <c r="Q98">
-        <v>-35.7034912</v>
+        <v>-36.49701715000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.397220260177339</v>
+        <v>1.847693680236453</v>
       </c>
       <c r="T98">
-        <v>26.34169626806383</v>
+        <v>35.12226169075178</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1055908285040962</v>
+        <v>0.1045022632617859</v>
       </c>
       <c r="W98">
-        <v>0.2109016826387341</v>
+        <v>0.2111583663228709</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4223633140163847</v>
+        <v>0.4180090530471435</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2602544257402784</v>
+        <v>0.2621544257402784</v>
       </c>
       <c r="C99">
-        <v>-235.6532205568467</v>
+        <v>-241.1786975822557</v>
       </c>
       <c r="D99">
-        <v>129.7857794431534</v>
+        <v>128.7473024177443</v>
       </c>
       <c r="E99">
-        <v>420.639</v>
+        <v>425.126</v>
       </c>
       <c r="F99">
-        <v>435.239</v>
+        <v>439.7260000000001</v>
       </c>
       <c r="G99">
         <v>69.8</v>
@@ -9533,37 +9533,37 @@
         <v>42.9</v>
       </c>
       <c r="M99">
-        <v>102.6293562</v>
+        <v>103.6873908</v>
       </c>
       <c r="N99">
-        <v>-59.72935620000002</v>
+        <v>-60.78739080000002</v>
       </c>
       <c r="O99">
-        <v>-14.93233905</v>
+        <v>-15.1968477</v>
       </c>
       <c r="P99">
-        <v>-44.79701715000002</v>
+        <v>-45.59054310000001</v>
       </c>
       <c r="Q99">
-        <v>-36.49701715000001</v>
+        <v>-37.29054310000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.847693680236453</v>
+        <v>2.748640520354678</v>
       </c>
       <c r="T99">
-        <v>35.12226169075178</v>
+        <v>52.68339253612767</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1045022632617859</v>
+        <v>0.1034359136366656</v>
       </c>
       <c r="W99">
-        <v>0.2111583663228709</v>
+        <v>0.2114098115644742</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4180090530471435</v>
+        <v>0.4137436545466625</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2621544257402784</v>
+        <v>0.2640544257402784</v>
       </c>
       <c r="C100">
-        <v>-241.1786975822557</v>
+        <v>-246.6876878404335</v>
       </c>
       <c r="D100">
-        <v>128.7473024177443</v>
+        <v>127.7253121595666</v>
       </c>
       <c r="E100">
-        <v>425.126</v>
+        <v>429.613</v>
       </c>
       <c r="F100">
-        <v>439.7260000000001</v>
+        <v>444.213</v>
       </c>
       <c r="G100">
         <v>69.8</v>
@@ -9615,37 +9615,37 @@
         <v>42.9</v>
       </c>
       <c r="M100">
-        <v>103.6873908</v>
+        <v>104.7454254</v>
       </c>
       <c r="N100">
-        <v>-60.78739080000002</v>
+        <v>-61.84542540000002</v>
       </c>
       <c r="O100">
-        <v>-15.1968477</v>
+        <v>-15.46135635</v>
       </c>
       <c r="P100">
-        <v>-45.59054310000001</v>
+        <v>-46.38406905000002</v>
       </c>
       <c r="Q100">
-        <v>-37.29054310000001</v>
+        <v>-38.08406905000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.748640520354678</v>
+        <v>5.451481040709356</v>
       </c>
       <c r="T100">
-        <v>52.68339253612767</v>
+        <v>105.3667850722553</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1034359136366656</v>
+        <v>0.1023911064282145</v>
       </c>
       <c r="W100">
-        <v>0.2114098115644742</v>
+        <v>0.211656177104227</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4137436545466625</v>
+        <v>0.4095644257128578</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2640544257402784</v>
-      </c>
-      <c r="C101">
-        <v>-246.6876878404335</v>
-      </c>
-      <c r="D101">
-        <v>127.7253121595666</v>
-      </c>
-      <c r="E101">
-        <v>429.613</v>
-      </c>
-      <c r="F101">
-        <v>444.213</v>
-      </c>
-      <c r="G101">
-        <v>69.8</v>
-      </c>
-      <c r="H101">
-        <v>434.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>51.2</v>
-      </c>
-      <c r="K101">
-        <v>8.300000000000004</v>
-      </c>
-      <c r="L101">
-        <v>42.9</v>
-      </c>
-      <c r="M101">
-        <v>104.7454254</v>
-      </c>
-      <c r="N101">
-        <v>-61.84542540000002</v>
-      </c>
-      <c r="O101">
-        <v>-15.46135635</v>
-      </c>
-      <c r="P101">
-        <v>-46.38406905000002</v>
-      </c>
-      <c r="Q101">
-        <v>-38.08406905000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.451481040709356</v>
-      </c>
-      <c r="T101">
-        <v>105.3667850722553</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1023911064282145</v>
-      </c>
-      <c r="W101">
-        <v>0.211656177104227</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4095644257128578</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
